--- a/AAII_Financials/Yearly/SSDOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSDOY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="92">
   <si>
     <t>SSDOY</t>
   </si>
@@ -656,196 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42094</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41729</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41364</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40999</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7087200</v>
+        <v>6558300</v>
       </c>
       <c r="E8" s="3">
-        <v>6706200</v>
+        <v>7194000</v>
       </c>
       <c r="F8" s="3">
-        <v>6114700</v>
+        <v>6807200</v>
       </c>
       <c r="G8" s="3">
-        <v>7513500</v>
+        <v>6206800</v>
       </c>
       <c r="H8" s="3">
-        <v>7269600</v>
+        <v>7626600</v>
       </c>
       <c r="I8" s="3">
-        <v>6673600</v>
+        <v>7379100</v>
       </c>
       <c r="J8" s="3">
+        <v>6774100</v>
+      </c>
+      <c r="K8" s="3">
         <v>5646000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5410100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6851400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7323300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6126700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6052800</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2146000</v>
+        <v>1750200</v>
       </c>
       <c r="E9" s="3">
-        <v>1804800</v>
+        <v>2178300</v>
       </c>
       <c r="F9" s="3">
-        <v>1583000</v>
+        <v>1832000</v>
       </c>
       <c r="G9" s="3">
-        <v>1692200</v>
+        <v>1606800</v>
       </c>
       <c r="H9" s="3">
-        <v>1540000</v>
+        <v>1717600</v>
       </c>
       <c r="I9" s="3">
-        <v>1536000</v>
+        <v>1563200</v>
       </c>
       <c r="J9" s="3">
+        <v>1559100</v>
+      </c>
+      <c r="K9" s="3">
         <v>1378200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1389700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1730600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1821700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1507700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1445700</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4941200</v>
+        <v>4808100</v>
       </c>
       <c r="E10" s="3">
-        <v>4901400</v>
+        <v>5015700</v>
       </c>
       <c r="F10" s="3">
-        <v>4531700</v>
+        <v>4975200</v>
       </c>
       <c r="G10" s="3">
-        <v>5821300</v>
+        <v>4600000</v>
       </c>
       <c r="H10" s="3">
-        <v>5729600</v>
+        <v>5909000</v>
       </c>
       <c r="I10" s="3">
-        <v>5137600</v>
+        <v>5815900</v>
       </c>
       <c r="J10" s="3">
+        <v>5215000</v>
+      </c>
+      <c r="K10" s="3">
         <v>4267900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4020400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5120800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5501600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4618900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4607000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -862,50 +874,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="3">
-        <v>170100</v>
+      <c r="E12" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="F12" s="3">
-        <v>179200</v>
+        <v>172700</v>
       </c>
       <c r="G12" s="3">
-        <v>210500</v>
+        <v>181900</v>
       </c>
       <c r="H12" s="3">
-        <v>193400</v>
+        <v>213600</v>
       </c>
       <c r="I12" s="3">
-        <v>160900</v>
+        <v>196300</v>
       </c>
       <c r="J12" s="3">
+        <v>163300</v>
+      </c>
+      <c r="K12" s="3">
         <v>121300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>80100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>125300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>130100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>123500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>130100</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -945,51 +961,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-114600</v>
+        <v>6200</v>
       </c>
       <c r="E14" s="3">
-        <v>-527400</v>
+        <v>-116400</v>
       </c>
       <c r="F14" s="3">
-        <v>123100</v>
+        <v>-535400</v>
       </c>
       <c r="G14" s="3">
-        <v>24000</v>
+        <v>125000</v>
       </c>
       <c r="H14" s="3">
-        <v>60600</v>
+        <v>24400</v>
       </c>
       <c r="I14" s="3">
-        <v>523900</v>
+        <v>61500</v>
       </c>
       <c r="J14" s="3">
+        <v>531800</v>
+      </c>
+      <c r="K14" s="3">
         <v>31800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>17400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>52300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>63400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>315400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1500</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1029,9 +1051,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>6778000</v>
+        <v>6368700</v>
       </c>
       <c r="E17" s="3">
-        <v>6038400</v>
+        <v>6880100</v>
       </c>
       <c r="F17" s="3">
-        <v>6138500</v>
+        <v>6129300</v>
       </c>
       <c r="G17" s="3">
-        <v>6781700</v>
+        <v>6230900</v>
       </c>
       <c r="H17" s="3">
-        <v>6610800</v>
+        <v>6883800</v>
       </c>
       <c r="I17" s="3">
-        <v>6663400</v>
+        <v>6710300</v>
       </c>
       <c r="J17" s="3">
+        <v>6763800</v>
+      </c>
+      <c r="K17" s="3">
         <v>5433600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5160500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6660400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6909600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6206600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5707100</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>309200</v>
+        <v>189600</v>
       </c>
       <c r="E18" s="3">
-        <v>667800</v>
+        <v>313900</v>
       </c>
       <c r="F18" s="3">
-        <v>-23800</v>
+        <v>677800</v>
       </c>
       <c r="G18" s="3">
-        <v>731800</v>
+        <v>-24100</v>
       </c>
       <c r="H18" s="3">
-        <v>658900</v>
+        <v>742800</v>
       </c>
       <c r="I18" s="3">
-        <v>10200</v>
+        <v>668800</v>
       </c>
       <c r="J18" s="3">
+        <v>10300</v>
+      </c>
+      <c r="K18" s="3">
         <v>212400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>249600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>191000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>413600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-79900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>345600</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1147,218 +1179,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>41100</v>
+        <v>19600</v>
       </c>
       <c r="E20" s="3">
-        <v>24600</v>
+        <v>41700</v>
       </c>
       <c r="F20" s="3">
-        <v>25000</v>
+        <v>24900</v>
       </c>
       <c r="G20" s="3">
-        <v>-3600</v>
+        <v>25400</v>
       </c>
       <c r="H20" s="3">
-        <v>38900</v>
+        <v>-3700</v>
       </c>
       <c r="I20" s="3">
-        <v>252400</v>
+        <v>39400</v>
       </c>
       <c r="J20" s="3">
+        <v>256200</v>
+      </c>
+      <c r="K20" s="3">
         <v>124100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>60300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>251600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>87600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>37800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>16000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>850800</v>
+        <v>720300</v>
       </c>
       <c r="E21" s="3">
-        <v>1240500</v>
+        <v>868200</v>
       </c>
       <c r="F21" s="3">
-        <v>447100</v>
+        <v>1264200</v>
       </c>
       <c r="G21" s="3">
-        <v>1114300</v>
+        <v>457900</v>
       </c>
       <c r="H21" s="3">
-        <v>987500</v>
+        <v>1134600</v>
       </c>
       <c r="I21" s="3">
-        <v>552400</v>
+        <v>1005100</v>
       </c>
       <c r="J21" s="3">
+        <v>563400</v>
+      </c>
+      <c r="K21" s="3">
         <v>596900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>562100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>778900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>867500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>297600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>682800</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3">
-        <v>15500</v>
+      <c r="D22" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="E22" s="3">
-        <v>34300</v>
+        <v>15700</v>
       </c>
       <c r="F22" s="3">
-        <v>14800</v>
+        <v>34800</v>
       </c>
       <c r="G22" s="3">
-        <v>15200</v>
+        <v>15000</v>
       </c>
       <c r="H22" s="3">
-        <v>5100</v>
+        <v>15400</v>
       </c>
       <c r="I22" s="3">
-        <v>6600</v>
+        <v>5200</v>
       </c>
       <c r="J22" s="3">
+        <v>6700</v>
+      </c>
+      <c r="K22" s="3">
         <v>5400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>10600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>16600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>16100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>16200</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>334800</v>
+        <v>209200</v>
       </c>
       <c r="E23" s="3">
-        <v>658100</v>
+        <v>339900</v>
       </c>
       <c r="F23" s="3">
-        <v>-13500</v>
+        <v>668000</v>
       </c>
       <c r="G23" s="3">
-        <v>713000</v>
+        <v>-13700</v>
       </c>
       <c r="H23" s="3">
-        <v>692600</v>
+        <v>723700</v>
       </c>
       <c r="I23" s="3">
-        <v>256000</v>
+        <v>703000</v>
       </c>
       <c r="J23" s="3">
+        <v>259900</v>
+      </c>
+      <c r="K23" s="3">
         <v>331100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>304100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>432000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>484600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-58200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>345500</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>85300</v>
+        <v>46200</v>
       </c>
       <c r="E24" s="3">
-        <v>329700</v>
+        <v>86600</v>
       </c>
       <c r="F24" s="3">
-        <v>47000</v>
+        <v>334700</v>
       </c>
       <c r="G24" s="3">
-        <v>199700</v>
+        <v>47700</v>
       </c>
       <c r="H24" s="3">
-        <v>261600</v>
+        <v>202700</v>
       </c>
       <c r="I24" s="3">
-        <v>87600</v>
+        <v>265600</v>
       </c>
       <c r="J24" s="3">
+        <v>89000</v>
+      </c>
+      <c r="K24" s="3">
         <v>105800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>122600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>112900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>208400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>56700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>194100</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>249600</v>
+        <v>163000</v>
       </c>
       <c r="E26" s="3">
-        <v>328300</v>
+        <v>253300</v>
       </c>
       <c r="F26" s="3">
-        <v>-60600</v>
+        <v>333300</v>
       </c>
       <c r="G26" s="3">
-        <v>513300</v>
+        <v>-61500</v>
       </c>
       <c r="H26" s="3">
-        <v>431000</v>
+        <v>521000</v>
       </c>
       <c r="I26" s="3">
-        <v>168400</v>
+        <v>437500</v>
       </c>
       <c r="J26" s="3">
+        <v>170900</v>
+      </c>
+      <c r="K26" s="3">
         <v>225300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>181500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>319200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>276200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-114900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>151300</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>227100</v>
+        <v>146600</v>
       </c>
       <c r="E27" s="3">
-        <v>295100</v>
+        <v>230500</v>
       </c>
       <c r="F27" s="3">
-        <v>-77400</v>
+        <v>299500</v>
       </c>
       <c r="G27" s="3">
-        <v>488500</v>
+        <v>-78600</v>
       </c>
       <c r="H27" s="3">
-        <v>407700</v>
+        <v>495800</v>
       </c>
       <c r="I27" s="3">
-        <v>151100</v>
+        <v>413900</v>
       </c>
       <c r="J27" s="3">
+        <v>153300</v>
+      </c>
+      <c r="K27" s="3">
         <v>213200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>164600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>296600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>251300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-132800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>128700</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1650,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-41100</v>
+        <v>-19600</v>
       </c>
       <c r="E32" s="3">
-        <v>-24600</v>
+        <v>-41700</v>
       </c>
       <c r="F32" s="3">
-        <v>-25000</v>
+        <v>-24900</v>
       </c>
       <c r="G32" s="3">
-        <v>3600</v>
+        <v>-25400</v>
       </c>
       <c r="H32" s="3">
-        <v>-38900</v>
+        <v>3700</v>
       </c>
       <c r="I32" s="3">
-        <v>-252400</v>
+        <v>-39400</v>
       </c>
       <c r="J32" s="3">
+        <v>-256200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-124100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-60300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-251600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-87600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-37800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-16000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>227100</v>
+        <v>146600</v>
       </c>
       <c r="E33" s="3">
-        <v>295100</v>
+        <v>230500</v>
       </c>
       <c r="F33" s="3">
-        <v>-77400</v>
+        <v>299500</v>
       </c>
       <c r="G33" s="3">
-        <v>488500</v>
+        <v>-78600</v>
       </c>
       <c r="H33" s="3">
-        <v>407700</v>
+        <v>495800</v>
       </c>
       <c r="I33" s="3">
-        <v>151100</v>
+        <v>413900</v>
       </c>
       <c r="J33" s="3">
+        <v>153300</v>
+      </c>
+      <c r="K33" s="3">
         <v>213200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>164600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>296600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>251300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-132800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>128700</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>227100</v>
+        <v>146600</v>
       </c>
       <c r="E35" s="3">
-        <v>295100</v>
+        <v>230500</v>
       </c>
       <c r="F35" s="3">
-        <v>-77400</v>
+        <v>299500</v>
       </c>
       <c r="G35" s="3">
-        <v>488500</v>
+        <v>-78600</v>
       </c>
       <c r="H35" s="3">
-        <v>407700</v>
+        <v>495800</v>
       </c>
       <c r="I35" s="3">
-        <v>151100</v>
+        <v>413900</v>
       </c>
       <c r="J35" s="3">
+        <v>153300</v>
+      </c>
+      <c r="K35" s="3">
         <v>213200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>164600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>296600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>251300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-132800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>128700</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42094</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41729</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41364</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40999</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1902,386 +1987,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>790400</v>
+        <v>705600</v>
       </c>
       <c r="E41" s="3">
-        <v>3220800</v>
+        <v>802300</v>
       </c>
       <c r="F41" s="3">
-        <v>863300</v>
+        <v>3269300</v>
       </c>
       <c r="G41" s="3">
-        <v>732700</v>
+        <v>876300</v>
       </c>
       <c r="H41" s="3">
-        <v>835900</v>
+        <v>743700</v>
       </c>
       <c r="I41" s="3">
-        <v>1106900</v>
+        <v>848500</v>
       </c>
       <c r="J41" s="3">
+        <v>1123500</v>
+      </c>
+      <c r="K41" s="3">
         <v>797600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>827900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>912700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>920400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>536300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>595400</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>122800</v>
+        <v>148000</v>
       </c>
       <c r="E42" s="3">
-        <v>109100</v>
+        <v>124700</v>
       </c>
       <c r="F42" s="3">
-        <v>139400</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>91</v>
+        <v>110700</v>
+      </c>
+      <c r="G42" s="3">
+        <v>141500</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I42" s="3">
-        <v>51700</v>
+      <c r="I42" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="J42" s="3">
+        <v>52400</v>
+      </c>
+      <c r="K42" s="3">
         <v>52500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>54500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>160900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>318400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>288700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>237000</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>1208900</v>
+        <v>1008900</v>
       </c>
       <c r="E43" s="3">
-        <v>3085400</v>
+        <v>1227100</v>
       </c>
       <c r="F43" s="3">
-        <v>936800</v>
+        <v>3131800</v>
       </c>
       <c r="G43" s="3">
-        <v>1129900</v>
+        <v>950900</v>
       </c>
       <c r="H43" s="3">
-        <v>1092300</v>
+        <v>1146900</v>
       </c>
       <c r="I43" s="3">
-        <v>1064600</v>
+        <v>1108700</v>
       </c>
       <c r="J43" s="3">
+        <v>1080600</v>
+      </c>
+      <c r="K43" s="3">
         <v>895300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>889300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1147200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1314600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1059600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>992900</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>869500</v>
+        <v>1008600</v>
       </c>
       <c r="E44" s="3">
-        <v>2736000</v>
+        <v>882500</v>
       </c>
       <c r="F44" s="3">
-        <v>1129000</v>
+        <v>2777200</v>
       </c>
       <c r="G44" s="3">
-        <v>1202500</v>
+        <v>1146000</v>
       </c>
       <c r="H44" s="3">
-        <v>994600</v>
+        <v>1220600</v>
       </c>
       <c r="I44" s="3">
-        <v>862900</v>
+        <v>1009600</v>
       </c>
       <c r="J44" s="3">
+        <v>875900</v>
+      </c>
+      <c r="K44" s="3">
         <v>1536100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>751000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>940000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>867200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1528700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>637800</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>489300</v>
+        <v>296800</v>
       </c>
       <c r="E45" s="3">
-        <v>312400</v>
+        <v>496600</v>
       </c>
       <c r="F45" s="3">
-        <v>349500</v>
+        <v>317100</v>
       </c>
       <c r="G45" s="3">
-        <v>471500</v>
+        <v>354800</v>
       </c>
       <c r="H45" s="3">
-        <v>481400</v>
+        <v>478600</v>
       </c>
       <c r="I45" s="3">
-        <v>408200</v>
+        <v>488700</v>
       </c>
       <c r="J45" s="3">
+        <v>414400</v>
+      </c>
+      <c r="K45" s="3">
         <v>354300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>388900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>495900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>448300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>358500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>333100</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>3480900</v>
+        <v>3167900</v>
       </c>
       <c r="E46" s="3">
-        <v>3405800</v>
+        <v>3533300</v>
       </c>
       <c r="F46" s="3">
-        <v>3418000</v>
+        <v>3457100</v>
       </c>
       <c r="G46" s="3">
-        <v>3536600</v>
+        <v>3469500</v>
       </c>
       <c r="H46" s="3">
-        <v>3207100</v>
+        <v>3589900</v>
       </c>
       <c r="I46" s="3">
-        <v>3494300</v>
+        <v>3255400</v>
       </c>
       <c r="J46" s="3">
+        <v>3546900</v>
+      </c>
+      <c r="K46" s="3">
         <v>2867800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2911700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3656800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3868900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3007400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2796000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>665600</v>
+        <v>766800</v>
       </c>
       <c r="E47" s="3">
-        <v>904800</v>
+        <v>675600</v>
       </c>
       <c r="F47" s="3">
-        <v>88900</v>
+        <v>918500</v>
       </c>
       <c r="G47" s="3">
-        <v>92200</v>
+        <v>90200</v>
       </c>
       <c r="H47" s="3">
-        <v>305300</v>
+        <v>93600</v>
       </c>
       <c r="I47" s="3">
-        <v>173500</v>
+        <v>309900</v>
       </c>
       <c r="J47" s="3">
+        <v>176100</v>
+      </c>
+      <c r="K47" s="3">
         <v>332000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>197000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>257000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>257900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>551200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>243000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>2872600</v>
+        <v>2712100</v>
       </c>
       <c r="E48" s="3">
-        <v>8586500</v>
+        <v>2915800</v>
       </c>
       <c r="F48" s="3">
-        <v>2264500</v>
+        <v>7854200</v>
       </c>
       <c r="G48" s="3">
-        <v>2090000</v>
+        <v>2298600</v>
       </c>
       <c r="H48" s="3">
-        <v>1561600</v>
+        <v>2121500</v>
       </c>
       <c r="I48" s="3">
-        <v>1053600</v>
+        <v>1585100</v>
       </c>
       <c r="J48" s="3">
+        <v>1069500</v>
+      </c>
+      <c r="K48" s="3">
         <v>1037100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>952100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1206800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1296200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1155400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1151300</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>1202500</v>
+        <v>1346700</v>
       </c>
       <c r="E49" s="3">
-        <v>2701300</v>
+        <v>1220600</v>
       </c>
       <c r="F49" s="3">
-        <v>1602800</v>
+        <v>2741900</v>
       </c>
       <c r="G49" s="3">
-        <v>1654700</v>
+        <v>1627000</v>
       </c>
       <c r="H49" s="3">
-        <v>1098300</v>
+        <v>1679700</v>
       </c>
       <c r="I49" s="3">
-        <v>1119400</v>
+        <v>1114800</v>
       </c>
       <c r="J49" s="3">
+        <v>1136300</v>
+      </c>
+      <c r="K49" s="3">
         <v>1635700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1144300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1472300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1602300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1362300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1540200</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2363,51 +2479,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>461400</v>
+        <v>468600</v>
       </c>
       <c r="E52" s="3">
-        <v>747900</v>
+        <v>468300</v>
       </c>
       <c r="F52" s="3">
-        <v>621800</v>
+        <v>759200</v>
       </c>
       <c r="G52" s="3">
-        <v>719300</v>
+        <v>631200</v>
       </c>
       <c r="H52" s="3">
-        <v>684400</v>
+        <v>730100</v>
       </c>
       <c r="I52" s="3">
-        <v>463400</v>
+        <v>694700</v>
       </c>
       <c r="J52" s="3">
+        <v>470300</v>
+      </c>
+      <c r="K52" s="3">
         <v>498400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>527500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>663300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>675700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>668600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>662000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>8682900</v>
+        <v>8462000</v>
       </c>
       <c r="E54" s="3">
-        <v>8638500</v>
+        <v>8813600</v>
       </c>
       <c r="F54" s="3">
-        <v>7996100</v>
+        <v>8768600</v>
       </c>
       <c r="G54" s="3">
-        <v>8092800</v>
+        <v>8116500</v>
       </c>
       <c r="H54" s="3">
-        <v>6703900</v>
+        <v>8214700</v>
       </c>
       <c r="I54" s="3">
-        <v>6304200</v>
+        <v>6804800</v>
       </c>
       <c r="J54" s="3">
+        <v>6399100</v>
+      </c>
+      <c r="K54" s="3">
         <v>6205700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5732600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7256200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7700900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6469000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6392600</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2526,260 +2655,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>709400</v>
+        <v>1203300</v>
       </c>
       <c r="E57" s="3">
-        <v>2495900</v>
+        <v>720000</v>
       </c>
       <c r="F57" s="3">
-        <v>510800</v>
+        <v>2533500</v>
       </c>
       <c r="G57" s="3">
-        <v>643700</v>
+        <v>518500</v>
       </c>
       <c r="H57" s="3">
-        <v>679200</v>
+        <v>653400</v>
       </c>
       <c r="I57" s="3">
-        <v>577900</v>
+        <v>689400</v>
       </c>
       <c r="J57" s="3">
+        <v>586600</v>
+      </c>
+      <c r="K57" s="3">
         <v>553700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>441800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>532500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>489600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>393600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>428500</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>330300</v>
+        <v>484700</v>
       </c>
       <c r="E58" s="3">
-        <v>547200</v>
+        <v>335300</v>
       </c>
       <c r="F58" s="3">
-        <v>518400</v>
+        <v>555500</v>
       </c>
       <c r="G58" s="3">
-        <v>975600</v>
+        <v>526200</v>
       </c>
       <c r="H58" s="3">
-        <v>100900</v>
+        <v>990300</v>
       </c>
       <c r="I58" s="3">
-        <v>70800</v>
+        <v>102500</v>
       </c>
       <c r="J58" s="3">
+        <v>71900</v>
+      </c>
+      <c r="K58" s="3">
         <v>109900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>134700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>666200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>615500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>356100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>86300</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>1547000</v>
+        <v>794700</v>
       </c>
       <c r="E59" s="3">
-        <v>2794400</v>
+        <v>1570300</v>
       </c>
       <c r="F59" s="3">
-        <v>1314600</v>
+        <v>2836400</v>
       </c>
       <c r="G59" s="3">
-        <v>1463500</v>
+        <v>1334400</v>
       </c>
       <c r="H59" s="3">
-        <v>1477000</v>
+        <v>1485500</v>
       </c>
       <c r="I59" s="3">
-        <v>1286100</v>
+        <v>1499300</v>
       </c>
       <c r="J59" s="3">
+        <v>1305400</v>
+      </c>
+      <c r="K59" s="3">
         <v>974300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>889600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1139400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1295300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>942800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>946200</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>2586700</v>
+        <v>2482600</v>
       </c>
       <c r="E60" s="3">
-        <v>2746000</v>
+        <v>2625600</v>
       </c>
       <c r="F60" s="3">
-        <v>2343800</v>
+        <v>2787400</v>
       </c>
       <c r="G60" s="3">
-        <v>3082800</v>
+        <v>2379100</v>
       </c>
       <c r="H60" s="3">
-        <v>2257200</v>
+        <v>3129200</v>
       </c>
       <c r="I60" s="3">
-        <v>1934800</v>
+        <v>2291200</v>
       </c>
       <c r="J60" s="3">
+        <v>1963900</v>
+      </c>
+      <c r="K60" s="3">
         <v>1638000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1466100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2338000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2400400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1692500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1461000</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>1643000</v>
+        <v>1409100</v>
       </c>
       <c r="E61" s="3">
-        <v>1758400</v>
+        <v>1667800</v>
       </c>
       <c r="F61" s="3">
-        <v>1983100</v>
+        <v>1784900</v>
       </c>
       <c r="G61" s="3">
-        <v>1006200</v>
+        <v>2013000</v>
       </c>
       <c r="H61" s="3">
-        <v>761800</v>
+        <v>1021400</v>
       </c>
       <c r="I61" s="3">
-        <v>862900</v>
+        <v>773300</v>
       </c>
       <c r="J61" s="3">
+        <v>875900</v>
+      </c>
+      <c r="K61" s="3">
         <v>690700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>479400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>275600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>882800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1313300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1555900</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>298200</v>
+        <v>254100</v>
       </c>
       <c r="E62" s="3">
-        <v>670700</v>
+        <v>302700</v>
       </c>
       <c r="F62" s="3">
-        <v>305400</v>
+        <v>680800</v>
       </c>
       <c r="G62" s="3">
-        <v>565200</v>
+        <v>310000</v>
       </c>
       <c r="H62" s="3">
-        <v>574200</v>
+        <v>573700</v>
       </c>
       <c r="I62" s="3">
-        <v>546000</v>
+        <v>582900</v>
       </c>
       <c r="J62" s="3">
+        <v>554200</v>
+      </c>
+      <c r="K62" s="3">
         <v>1128900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>856600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1036100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>970500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>722700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>681700</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>4670600</v>
+        <v>4291700</v>
       </c>
       <c r="E66" s="3">
-        <v>5048300</v>
+        <v>4740900</v>
       </c>
       <c r="F66" s="3">
-        <v>4771100</v>
+        <v>5124300</v>
       </c>
       <c r="G66" s="3">
-        <v>4788100</v>
+        <v>4843000</v>
       </c>
       <c r="H66" s="3">
-        <v>3719000</v>
+        <v>4860200</v>
       </c>
       <c r="I66" s="3">
-        <v>3486700</v>
+        <v>3775000</v>
       </c>
       <c r="J66" s="3">
+        <v>3539200</v>
+      </c>
+      <c r="K66" s="3">
         <v>3591000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2949600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3838800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4438300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3866200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3810000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3131,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>2622000</v>
+        <v>2562600</v>
       </c>
       <c r="E72" s="3">
-        <v>4910800</v>
+        <v>2661500</v>
       </c>
       <c r="F72" s="3">
-        <v>2265700</v>
+        <v>4984700</v>
       </c>
       <c r="G72" s="3">
-        <v>2474700</v>
+        <v>2299800</v>
       </c>
       <c r="H72" s="3">
-        <v>2124500</v>
+        <v>2512000</v>
       </c>
       <c r="I72" s="3">
-        <v>1809800</v>
+        <v>2156500</v>
       </c>
       <c r="J72" s="3">
+        <v>1837000</v>
+      </c>
+      <c r="K72" s="3">
         <v>1718600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1664700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1936400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1964200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1738600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2001100</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>4012300</v>
+        <v>4170400</v>
       </c>
       <c r="E76" s="3">
-        <v>3590200</v>
+        <v>4072700</v>
       </c>
       <c r="F76" s="3">
-        <v>3225000</v>
+        <v>3644300</v>
       </c>
       <c r="G76" s="3">
-        <v>3304700</v>
+        <v>3273500</v>
       </c>
       <c r="H76" s="3">
-        <v>2984900</v>
+        <v>3354500</v>
       </c>
       <c r="I76" s="3">
-        <v>2817500</v>
+        <v>3029900</v>
       </c>
       <c r="J76" s="3">
+        <v>2859900</v>
+      </c>
+      <c r="K76" s="3">
         <v>2614700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2783000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3417400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3262600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2602800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2582600</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42094</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41729</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41364</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40999</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>227100</v>
+        <v>146600</v>
       </c>
       <c r="E81" s="3">
-        <v>295100</v>
+        <v>230500</v>
       </c>
       <c r="F81" s="3">
-        <v>-77400</v>
+        <v>299500</v>
       </c>
       <c r="G81" s="3">
-        <v>488500</v>
+        <v>-78600</v>
       </c>
       <c r="H81" s="3">
-        <v>407700</v>
+        <v>495800</v>
       </c>
       <c r="I81" s="3">
-        <v>151100</v>
+        <v>413900</v>
       </c>
       <c r="J81" s="3">
+        <v>153300</v>
+      </c>
+      <c r="K81" s="3">
         <v>213200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>164600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>296600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>251300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-132800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>128700</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3491,50 +3688,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>502800</v>
+        <v>508800</v>
       </c>
       <c r="E83" s="3">
-        <v>550600</v>
+        <v>510300</v>
       </c>
       <c r="F83" s="3">
-        <v>447900</v>
+        <v>558900</v>
       </c>
       <c r="G83" s="3">
-        <v>387800</v>
+        <v>454600</v>
       </c>
       <c r="H83" s="3">
-        <v>291100</v>
+        <v>393700</v>
       </c>
       <c r="I83" s="3">
-        <v>291200</v>
+        <v>295500</v>
       </c>
       <c r="J83" s="3">
+        <v>295500</v>
+      </c>
+      <c r="K83" s="3">
         <v>261600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>261900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>335500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>367000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>339300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>321100</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>307000</v>
+        <v>603500</v>
       </c>
       <c r="E89" s="3">
-        <v>891400</v>
+        <v>311600</v>
       </c>
       <c r="F89" s="3">
-        <v>425300</v>
+        <v>904800</v>
       </c>
       <c r="G89" s="3">
-        <v>501600</v>
+        <v>431700</v>
       </c>
       <c r="H89" s="3">
-        <v>614700</v>
+        <v>509100</v>
       </c>
       <c r="I89" s="3">
-        <v>633400</v>
+        <v>624000</v>
       </c>
       <c r="J89" s="3">
+        <v>642900</v>
+      </c>
+      <c r="K89" s="3">
         <v>392600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>429200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>288100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>810300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>380100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>466500</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3803,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-241000</v>
+        <v>-180000</v>
       </c>
       <c r="E91" s="3">
-        <v>-499900</v>
+        <v>-244600</v>
       </c>
       <c r="F91" s="3">
-        <v>-374200</v>
+        <v>-507400</v>
       </c>
       <c r="G91" s="3">
-        <v>-612200</v>
+        <v>-379900</v>
       </c>
       <c r="H91" s="3">
-        <v>-535200</v>
+        <v>-621400</v>
       </c>
       <c r="I91" s="3">
-        <v>-239100</v>
+        <v>-543200</v>
       </c>
       <c r="J91" s="3">
+        <v>-242700</v>
+      </c>
+      <c r="K91" s="3">
         <v>-208300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-120100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-137500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-172600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-169600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-219400</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3928,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-274300</v>
+        <v>-239500</v>
       </c>
       <c r="E94" s="3">
-        <v>443100</v>
+        <v>-278400</v>
       </c>
       <c r="F94" s="3">
-        <v>-465400</v>
+        <v>449800</v>
       </c>
       <c r="G94" s="3">
-        <v>-1346700</v>
+        <v>-472400</v>
       </c>
       <c r="H94" s="3">
-        <v>-684700</v>
+        <v>-1367000</v>
       </c>
       <c r="I94" s="3">
-        <v>-7000</v>
+        <v>-695000</v>
       </c>
       <c r="J94" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-469000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-164000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>101600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-161400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-230800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-183300</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3989,50 +4221,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-145900</v>
+        <v>-282500</v>
       </c>
       <c r="E96" s="3">
-        <v>-106200</v>
+        <v>-148100</v>
       </c>
       <c r="F96" s="3">
-        <v>-132600</v>
+        <v>-107800</v>
       </c>
       <c r="G96" s="3">
-        <v>-146300</v>
+        <v>-134600</v>
       </c>
       <c r="H96" s="3">
-        <v>-92600</v>
+        <v>-148500</v>
       </c>
       <c r="I96" s="3">
-        <v>-59600</v>
+        <v>-94000</v>
       </c>
       <c r="J96" s="3">
+        <v>-60500</v>
+      </c>
+      <c r="K96" s="3">
         <v>-54500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-54700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-70400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-134000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-179900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-176400</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4156,133 +4398,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-348100</v>
+        <v>-509800</v>
       </c>
       <c r="E100" s="3">
-        <v>-1265400</v>
+        <v>-353300</v>
       </c>
       <c r="F100" s="3">
-        <v>311300</v>
+        <v>-1284500</v>
       </c>
       <c r="G100" s="3">
-        <v>754800</v>
+        <v>316000</v>
       </c>
       <c r="H100" s="3">
-        <v>-197400</v>
+        <v>766200</v>
       </c>
       <c r="I100" s="3">
-        <v>-352700</v>
+        <v>-200300</v>
       </c>
       <c r="J100" s="3">
+        <v>-358000</v>
+      </c>
+      <c r="K100" s="3">
         <v>148600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-213800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-514700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-456100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-223700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-314700</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>66600</v>
+        <v>49100</v>
       </c>
       <c r="E101" s="3">
-        <v>64700</v>
+        <v>67600</v>
       </c>
       <c r="F101" s="3">
-        <v>-13000</v>
+        <v>65700</v>
       </c>
       <c r="G101" s="3">
-        <v>-4600</v>
+        <v>-13200</v>
       </c>
       <c r="H101" s="3">
-        <v>-31900</v>
+        <v>-4700</v>
       </c>
       <c r="I101" s="3">
-        <v>16600</v>
+        <v>-32400</v>
       </c>
       <c r="J101" s="3">
+        <v>16800</v>
+      </c>
+      <c r="K101" s="3">
         <v>-17700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-22100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>42400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>94700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>49900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-18300</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-248800</v>
+        <v>-96700</v>
       </c>
       <c r="E102" s="3">
-        <v>133800</v>
+        <v>-252500</v>
       </c>
       <c r="F102" s="3">
-        <v>258200</v>
+        <v>135800</v>
       </c>
       <c r="G102" s="3">
-        <v>-95000</v>
+        <v>262100</v>
       </c>
       <c r="H102" s="3">
-        <v>-299200</v>
+        <v>-96400</v>
       </c>
       <c r="I102" s="3">
-        <v>290200</v>
+        <v>-303700</v>
       </c>
       <c r="J102" s="3">
+        <v>294600</v>
+      </c>
+      <c r="K102" s="3">
         <v>54400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>29200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-82400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>287400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-24600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-49800</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SSDOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSDOY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
   <si>
     <t>SSDOY</t>
   </si>
@@ -727,25 +727,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6558300</v>
+        <v>6208000</v>
       </c>
       <c r="E8" s="3">
-        <v>7194000</v>
+        <v>6809700</v>
       </c>
       <c r="F8" s="3">
-        <v>6807200</v>
+        <v>6443600</v>
       </c>
       <c r="G8" s="3">
-        <v>6206800</v>
+        <v>5875300</v>
       </c>
       <c r="H8" s="3">
-        <v>7626600</v>
+        <v>7219300</v>
       </c>
       <c r="I8" s="3">
-        <v>7379100</v>
+        <v>6985000</v>
       </c>
       <c r="J8" s="3">
-        <v>6774100</v>
+        <v>6412300</v>
       </c>
       <c r="K8" s="3">
         <v>5646000</v>
@@ -772,25 +772,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1750200</v>
+        <v>1656700</v>
       </c>
       <c r="E9" s="3">
-        <v>2178300</v>
+        <v>2086700</v>
       </c>
       <c r="F9" s="3">
-        <v>1832000</v>
+        <v>1734100</v>
       </c>
       <c r="G9" s="3">
-        <v>1606800</v>
+        <v>1521000</v>
       </c>
       <c r="H9" s="3">
-        <v>1717600</v>
+        <v>1625900</v>
       </c>
       <c r="I9" s="3">
-        <v>1563200</v>
+        <v>1479700</v>
       </c>
       <c r="J9" s="3">
-        <v>1559100</v>
+        <v>1475900</v>
       </c>
       <c r="K9" s="3">
         <v>1378200</v>
@@ -817,25 +817,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4808100</v>
+        <v>4551300</v>
       </c>
       <c r="E10" s="3">
-        <v>5015700</v>
+        <v>4723000</v>
       </c>
       <c r="F10" s="3">
-        <v>4975200</v>
+        <v>4709400</v>
       </c>
       <c r="G10" s="3">
-        <v>4600000</v>
+        <v>4354300</v>
       </c>
       <c r="H10" s="3">
-        <v>5909000</v>
+        <v>5593400</v>
       </c>
       <c r="I10" s="3">
-        <v>5815900</v>
+        <v>5505300</v>
       </c>
       <c r="J10" s="3">
-        <v>5215000</v>
+        <v>4936400</v>
       </c>
       <c r="K10" s="3">
         <v>4267900</v>
@@ -887,19 +887,19 @@
         <v>91</v>
       </c>
       <c r="F12" s="3">
-        <v>172700</v>
+        <v>163400</v>
       </c>
       <c r="G12" s="3">
-        <v>181900</v>
+        <v>172200</v>
       </c>
       <c r="H12" s="3">
-        <v>213600</v>
+        <v>202200</v>
       </c>
       <c r="I12" s="3">
-        <v>196300</v>
+        <v>185800</v>
       </c>
       <c r="J12" s="3">
-        <v>163300</v>
+        <v>154600</v>
       </c>
       <c r="K12" s="3">
         <v>121300</v>
@@ -971,25 +971,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>6200</v>
+        <v>32300</v>
       </c>
       <c r="E14" s="3">
-        <v>-116400</v>
+        <v>-110100</v>
       </c>
       <c r="F14" s="3">
-        <v>-535400</v>
+        <v>-506800</v>
       </c>
       <c r="G14" s="3">
-        <v>125000</v>
+        <v>118300</v>
       </c>
       <c r="H14" s="3">
-        <v>24400</v>
+        <v>23100</v>
       </c>
       <c r="I14" s="3">
-        <v>61500</v>
+        <v>58200</v>
       </c>
       <c r="J14" s="3">
-        <v>531800</v>
+        <v>503400</v>
       </c>
       <c r="K14" s="3">
         <v>31800</v>
@@ -1077,25 +1077,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>6368700</v>
+        <v>6028500</v>
       </c>
       <c r="E17" s="3">
-        <v>6880100</v>
+        <v>6512600</v>
       </c>
       <c r="F17" s="3">
-        <v>6129300</v>
+        <v>5801900</v>
       </c>
       <c r="G17" s="3">
-        <v>6230900</v>
+        <v>5898100</v>
       </c>
       <c r="H17" s="3">
-        <v>6883800</v>
+        <v>6516100</v>
       </c>
       <c r="I17" s="3">
-        <v>6710300</v>
+        <v>6351900</v>
       </c>
       <c r="J17" s="3">
-        <v>6763800</v>
+        <v>6402500</v>
       </c>
       <c r="K17" s="3">
         <v>5433600</v>
@@ -1122,25 +1122,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>189600</v>
+        <v>179500</v>
       </c>
       <c r="E18" s="3">
-        <v>313900</v>
+        <v>297100</v>
       </c>
       <c r="F18" s="3">
-        <v>677800</v>
+        <v>641600</v>
       </c>
       <c r="G18" s="3">
-        <v>-24100</v>
+        <v>-22900</v>
       </c>
       <c r="H18" s="3">
-        <v>742800</v>
+        <v>703200</v>
       </c>
       <c r="I18" s="3">
-        <v>668800</v>
+        <v>633100</v>
       </c>
       <c r="J18" s="3">
-        <v>10300</v>
+        <v>9800</v>
       </c>
       <c r="K18" s="3">
         <v>212400</v>
@@ -1186,25 +1186,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>19600</v>
+        <v>35000</v>
       </c>
       <c r="E20" s="3">
-        <v>41700</v>
+        <v>39500</v>
       </c>
       <c r="F20" s="3">
-        <v>24900</v>
+        <v>23600</v>
       </c>
       <c r="G20" s="3">
-        <v>25400</v>
+        <v>24000</v>
       </c>
       <c r="H20" s="3">
-        <v>-3700</v>
+        <v>-3500</v>
       </c>
       <c r="I20" s="3">
-        <v>39400</v>
+        <v>37300</v>
       </c>
       <c r="J20" s="3">
-        <v>256200</v>
+        <v>242500</v>
       </c>
       <c r="K20" s="3">
         <v>124100</v>
@@ -1231,25 +1231,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>720300</v>
+        <v>695400</v>
       </c>
       <c r="E21" s="3">
-        <v>868200</v>
+        <v>818900</v>
       </c>
       <c r="F21" s="3">
-        <v>1264200</v>
+        <v>1193400</v>
       </c>
       <c r="G21" s="3">
-        <v>457900</v>
+        <v>430800</v>
       </c>
       <c r="H21" s="3">
-        <v>1134600</v>
+        <v>1071800</v>
       </c>
       <c r="I21" s="3">
-        <v>1005100</v>
+        <v>949700</v>
       </c>
       <c r="J21" s="3">
-        <v>563400</v>
+        <v>531600</v>
       </c>
       <c r="K21" s="3">
         <v>596900</v>
@@ -1275,26 +1275,26 @@
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>91</v>
+      <c r="D22" s="3">
+        <v>16500</v>
       </c>
       <c r="E22" s="3">
-        <v>15700</v>
+        <v>14900</v>
       </c>
       <c r="F22" s="3">
-        <v>34800</v>
+        <v>32900</v>
       </c>
       <c r="G22" s="3">
-        <v>15000</v>
+        <v>14200</v>
       </c>
       <c r="H22" s="3">
-        <v>15400</v>
+        <v>14600</v>
       </c>
       <c r="I22" s="3">
-        <v>5200</v>
+        <v>4900</v>
       </c>
       <c r="J22" s="3">
-        <v>6700</v>
+        <v>6300</v>
       </c>
       <c r="K22" s="3">
         <v>5400</v>
@@ -1321,25 +1321,25 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>209200</v>
+        <v>198000</v>
       </c>
       <c r="E23" s="3">
-        <v>339900</v>
+        <v>321700</v>
       </c>
       <c r="F23" s="3">
-        <v>668000</v>
+        <v>632300</v>
       </c>
       <c r="G23" s="3">
-        <v>-13700</v>
+        <v>-13000</v>
       </c>
       <c r="H23" s="3">
-        <v>723700</v>
+        <v>685100</v>
       </c>
       <c r="I23" s="3">
-        <v>703000</v>
+        <v>665500</v>
       </c>
       <c r="J23" s="3">
-        <v>259900</v>
+        <v>246000</v>
       </c>
       <c r="K23" s="3">
         <v>331100</v>
@@ -1366,25 +1366,25 @@
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>46200</v>
+        <v>43800</v>
       </c>
       <c r="E24" s="3">
-        <v>86600</v>
+        <v>82000</v>
       </c>
       <c r="F24" s="3">
-        <v>334700</v>
+        <v>316800</v>
       </c>
       <c r="G24" s="3">
-        <v>47700</v>
+        <v>45200</v>
       </c>
       <c r="H24" s="3">
-        <v>202700</v>
+        <v>191900</v>
       </c>
       <c r="I24" s="3">
-        <v>265600</v>
+        <v>251400</v>
       </c>
       <c r="J24" s="3">
-        <v>89000</v>
+        <v>84200</v>
       </c>
       <c r="K24" s="3">
         <v>105800</v>
@@ -1456,25 +1456,25 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>163000</v>
+        <v>154200</v>
       </c>
       <c r="E26" s="3">
-        <v>253300</v>
+        <v>239800</v>
       </c>
       <c r="F26" s="3">
-        <v>333300</v>
+        <v>315500</v>
       </c>
       <c r="G26" s="3">
-        <v>-61500</v>
+        <v>-58200</v>
       </c>
       <c r="H26" s="3">
-        <v>521000</v>
+        <v>493200</v>
       </c>
       <c r="I26" s="3">
-        <v>437500</v>
+        <v>414100</v>
       </c>
       <c r="J26" s="3">
-        <v>170900</v>
+        <v>161800</v>
       </c>
       <c r="K26" s="3">
         <v>225300</v>
@@ -1501,25 +1501,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>146600</v>
+        <v>138800</v>
       </c>
       <c r="E27" s="3">
-        <v>230500</v>
+        <v>218200</v>
       </c>
       <c r="F27" s="3">
-        <v>299500</v>
+        <v>283500</v>
       </c>
       <c r="G27" s="3">
-        <v>-78600</v>
+        <v>-74400</v>
       </c>
       <c r="H27" s="3">
-        <v>495800</v>
+        <v>469300</v>
       </c>
       <c r="I27" s="3">
-        <v>413900</v>
+        <v>391800</v>
       </c>
       <c r="J27" s="3">
-        <v>153300</v>
+        <v>145100</v>
       </c>
       <c r="K27" s="3">
         <v>213200</v>
@@ -1726,25 +1726,25 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-19600</v>
+        <v>-35000</v>
       </c>
       <c r="E32" s="3">
-        <v>-41700</v>
+        <v>-39500</v>
       </c>
       <c r="F32" s="3">
-        <v>-24900</v>
+        <v>-23600</v>
       </c>
       <c r="G32" s="3">
-        <v>-25400</v>
+        <v>-24000</v>
       </c>
       <c r="H32" s="3">
-        <v>3700</v>
+        <v>3500</v>
       </c>
       <c r="I32" s="3">
-        <v>-39400</v>
+        <v>-37300</v>
       </c>
       <c r="J32" s="3">
-        <v>-256200</v>
+        <v>-242500</v>
       </c>
       <c r="K32" s="3">
         <v>-124100</v>
@@ -1771,25 +1771,25 @@
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>146600</v>
+        <v>138800</v>
       </c>
       <c r="E33" s="3">
-        <v>230500</v>
+        <v>218200</v>
       </c>
       <c r="F33" s="3">
-        <v>299500</v>
+        <v>283500</v>
       </c>
       <c r="G33" s="3">
-        <v>-78600</v>
+        <v>-74400</v>
       </c>
       <c r="H33" s="3">
-        <v>495800</v>
+        <v>469300</v>
       </c>
       <c r="I33" s="3">
-        <v>413900</v>
+        <v>391800</v>
       </c>
       <c r="J33" s="3">
-        <v>153300</v>
+        <v>145100</v>
       </c>
       <c r="K33" s="3">
         <v>213200</v>
@@ -1861,25 +1861,25 @@
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>146600</v>
+        <v>138800</v>
       </c>
       <c r="E35" s="3">
-        <v>230500</v>
+        <v>218200</v>
       </c>
       <c r="F35" s="3">
-        <v>299500</v>
+        <v>283500</v>
       </c>
       <c r="G35" s="3">
-        <v>-78600</v>
+        <v>-74400</v>
       </c>
       <c r="H35" s="3">
-        <v>495800</v>
+        <v>469300</v>
       </c>
       <c r="I35" s="3">
-        <v>413900</v>
+        <v>391800</v>
       </c>
       <c r="J35" s="3">
-        <v>153300</v>
+        <v>145100</v>
       </c>
       <c r="K35" s="3">
         <v>213200</v>
@@ -1994,25 +1994,25 @@
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>705600</v>
+        <v>667900</v>
       </c>
       <c r="E41" s="3">
-        <v>802300</v>
+        <v>759400</v>
       </c>
       <c r="F41" s="3">
-        <v>3269300</v>
+        <v>3094700</v>
       </c>
       <c r="G41" s="3">
-        <v>876300</v>
+        <v>829500</v>
       </c>
       <c r="H41" s="3">
-        <v>743700</v>
+        <v>704000</v>
       </c>
       <c r="I41" s="3">
-        <v>848500</v>
+        <v>803200</v>
       </c>
       <c r="J41" s="3">
-        <v>1123500</v>
+        <v>1063500</v>
       </c>
       <c r="K41" s="3">
         <v>797600</v>
@@ -2039,16 +2039,16 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>148000</v>
+        <v>140100</v>
       </c>
       <c r="E42" s="3">
-        <v>124700</v>
+        <v>118000</v>
       </c>
       <c r="F42" s="3">
-        <v>110700</v>
+        <v>104800</v>
       </c>
       <c r="G42" s="3">
-        <v>141500</v>
+        <v>134000</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>91</v>
@@ -2057,7 +2057,7 @@
         <v>91</v>
       </c>
       <c r="J42" s="3">
-        <v>52400</v>
+        <v>49600</v>
       </c>
       <c r="K42" s="3">
         <v>52500</v>
@@ -2084,25 +2084,25 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>1008900</v>
+        <v>955000</v>
       </c>
       <c r="E43" s="3">
-        <v>1227100</v>
+        <v>1161600</v>
       </c>
       <c r="F43" s="3">
-        <v>3131800</v>
+        <v>2964600</v>
       </c>
       <c r="G43" s="3">
-        <v>950900</v>
+        <v>900100</v>
       </c>
       <c r="H43" s="3">
-        <v>1146900</v>
+        <v>1085600</v>
       </c>
       <c r="I43" s="3">
-        <v>1108700</v>
+        <v>1049500</v>
       </c>
       <c r="J43" s="3">
-        <v>1080600</v>
+        <v>1022900</v>
       </c>
       <c r="K43" s="3">
         <v>895300</v>
@@ -2129,25 +2129,25 @@
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>1008600</v>
+        <v>954700</v>
       </c>
       <c r="E44" s="3">
-        <v>882500</v>
+        <v>835400</v>
       </c>
       <c r="F44" s="3">
-        <v>2777200</v>
+        <v>2628900</v>
       </c>
       <c r="G44" s="3">
-        <v>1146000</v>
+        <v>1084800</v>
       </c>
       <c r="H44" s="3">
-        <v>1220600</v>
+        <v>1155400</v>
       </c>
       <c r="I44" s="3">
-        <v>1009600</v>
+        <v>955600</v>
       </c>
       <c r="J44" s="3">
-        <v>875900</v>
+        <v>829100</v>
       </c>
       <c r="K44" s="3">
         <v>1536100</v>
@@ -2174,25 +2174,25 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>296800</v>
+        <v>281000</v>
       </c>
       <c r="E45" s="3">
-        <v>496600</v>
+        <v>470100</v>
       </c>
       <c r="F45" s="3">
-        <v>317100</v>
+        <v>300200</v>
       </c>
       <c r="G45" s="3">
-        <v>354800</v>
+        <v>335800</v>
       </c>
       <c r="H45" s="3">
-        <v>478600</v>
+        <v>453100</v>
       </c>
       <c r="I45" s="3">
-        <v>488700</v>
+        <v>462600</v>
       </c>
       <c r="J45" s="3">
-        <v>414400</v>
+        <v>392200</v>
       </c>
       <c r="K45" s="3">
         <v>354300</v>
@@ -2219,25 +2219,25 @@
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>3167900</v>
+        <v>2998700</v>
       </c>
       <c r="E46" s="3">
-        <v>3533300</v>
+        <v>3344600</v>
       </c>
       <c r="F46" s="3">
-        <v>3457100</v>
+        <v>3272400</v>
       </c>
       <c r="G46" s="3">
-        <v>3469500</v>
+        <v>3284200</v>
       </c>
       <c r="H46" s="3">
-        <v>3589900</v>
+        <v>3398100</v>
       </c>
       <c r="I46" s="3">
-        <v>3255400</v>
+        <v>3081500</v>
       </c>
       <c r="J46" s="3">
-        <v>3546900</v>
+        <v>3357400</v>
       </c>
       <c r="K46" s="3">
         <v>2867800</v>
@@ -2264,25 +2264,25 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>766800</v>
+        <v>725900</v>
       </c>
       <c r="E47" s="3">
-        <v>675600</v>
+        <v>639500</v>
       </c>
       <c r="F47" s="3">
-        <v>918500</v>
+        <v>869400</v>
       </c>
       <c r="G47" s="3">
-        <v>90200</v>
+        <v>85400</v>
       </c>
       <c r="H47" s="3">
-        <v>93600</v>
+        <v>88600</v>
       </c>
       <c r="I47" s="3">
-        <v>309900</v>
+        <v>293400</v>
       </c>
       <c r="J47" s="3">
-        <v>176100</v>
+        <v>166700</v>
       </c>
       <c r="K47" s="3">
         <v>332000</v>
@@ -2309,25 +2309,25 @@
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>2712100</v>
+        <v>2567200</v>
       </c>
       <c r="E48" s="3">
-        <v>2915800</v>
+        <v>2760100</v>
       </c>
       <c r="F48" s="3">
-        <v>7854200</v>
+        <v>7434700</v>
       </c>
       <c r="G48" s="3">
-        <v>2298600</v>
+        <v>2175900</v>
       </c>
       <c r="H48" s="3">
-        <v>2121500</v>
+        <v>2008100</v>
       </c>
       <c r="I48" s="3">
-        <v>1585100</v>
+        <v>1500500</v>
       </c>
       <c r="J48" s="3">
-        <v>1069500</v>
+        <v>1012400</v>
       </c>
       <c r="K48" s="3">
         <v>1037100</v>
@@ -2354,25 +2354,25 @@
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>1346700</v>
+        <v>1274800</v>
       </c>
       <c r="E49" s="3">
-        <v>1220600</v>
+        <v>1155400</v>
       </c>
       <c r="F49" s="3">
-        <v>2741900</v>
+        <v>2595500</v>
       </c>
       <c r="G49" s="3">
-        <v>1627000</v>
+        <v>1540100</v>
       </c>
       <c r="H49" s="3">
-        <v>1679700</v>
+        <v>1590000</v>
       </c>
       <c r="I49" s="3">
-        <v>1114800</v>
+        <v>1055300</v>
       </c>
       <c r="J49" s="3">
-        <v>1136300</v>
+        <v>1075600</v>
       </c>
       <c r="K49" s="3">
         <v>1635700</v>
@@ -2489,25 +2489,25 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>468600</v>
+        <v>443500</v>
       </c>
       <c r="E52" s="3">
-        <v>468300</v>
+        <v>443300</v>
       </c>
       <c r="F52" s="3">
-        <v>759200</v>
+        <v>718600</v>
       </c>
       <c r="G52" s="3">
-        <v>631200</v>
+        <v>597400</v>
       </c>
       <c r="H52" s="3">
-        <v>730100</v>
+        <v>691100</v>
       </c>
       <c r="I52" s="3">
-        <v>694700</v>
+        <v>657600</v>
       </c>
       <c r="J52" s="3">
-        <v>470300</v>
+        <v>445200</v>
       </c>
       <c r="K52" s="3">
         <v>498400</v>
@@ -2579,25 +2579,25 @@
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>8462000</v>
+        <v>8010100</v>
       </c>
       <c r="E54" s="3">
-        <v>8813600</v>
+        <v>8342900</v>
       </c>
       <c r="F54" s="3">
-        <v>8768600</v>
+        <v>8300200</v>
       </c>
       <c r="G54" s="3">
-        <v>8116500</v>
+        <v>7683000</v>
       </c>
       <c r="H54" s="3">
-        <v>8214700</v>
+        <v>7775900</v>
       </c>
       <c r="I54" s="3">
-        <v>6804800</v>
+        <v>6441400</v>
       </c>
       <c r="J54" s="3">
-        <v>6399100</v>
+        <v>6057300</v>
       </c>
       <c r="K54" s="3">
         <v>6205700</v>
@@ -2662,25 +2662,25 @@
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>1203300</v>
+        <v>640300</v>
       </c>
       <c r="E57" s="3">
-        <v>720000</v>
+        <v>681600</v>
       </c>
       <c r="F57" s="3">
-        <v>2533500</v>
+        <v>2398200</v>
       </c>
       <c r="G57" s="3">
-        <v>518500</v>
+        <v>490800</v>
       </c>
       <c r="H57" s="3">
-        <v>653400</v>
+        <v>618500</v>
       </c>
       <c r="I57" s="3">
-        <v>689400</v>
+        <v>652600</v>
       </c>
       <c r="J57" s="3">
-        <v>586600</v>
+        <v>555300</v>
       </c>
       <c r="K57" s="3">
         <v>553700</v>
@@ -2707,25 +2707,25 @@
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>484700</v>
+        <v>458800</v>
       </c>
       <c r="E58" s="3">
-        <v>335300</v>
+        <v>317400</v>
       </c>
       <c r="F58" s="3">
-        <v>555500</v>
+        <v>525800</v>
       </c>
       <c r="G58" s="3">
-        <v>526200</v>
+        <v>498100</v>
       </c>
       <c r="H58" s="3">
-        <v>990300</v>
+        <v>937400</v>
       </c>
       <c r="I58" s="3">
-        <v>102500</v>
+        <v>97000</v>
       </c>
       <c r="J58" s="3">
-        <v>71900</v>
+        <v>68000</v>
       </c>
       <c r="K58" s="3">
         <v>109900</v>
@@ -2752,25 +2752,25 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>794700</v>
+        <v>1250900</v>
       </c>
       <c r="E59" s="3">
-        <v>1570300</v>
+        <v>1486400</v>
       </c>
       <c r="F59" s="3">
-        <v>2836400</v>
+        <v>2684900</v>
       </c>
       <c r="G59" s="3">
-        <v>1334400</v>
+        <v>1263100</v>
       </c>
       <c r="H59" s="3">
-        <v>1485500</v>
+        <v>1406200</v>
       </c>
       <c r="I59" s="3">
-        <v>1499300</v>
+        <v>1419200</v>
       </c>
       <c r="J59" s="3">
-        <v>1305400</v>
+        <v>1235700</v>
       </c>
       <c r="K59" s="3">
         <v>974300</v>
@@ -2797,25 +2797,25 @@
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>2482600</v>
+        <v>2350000</v>
       </c>
       <c r="E60" s="3">
-        <v>2625600</v>
+        <v>2485400</v>
       </c>
       <c r="F60" s="3">
-        <v>2787400</v>
+        <v>2638500</v>
       </c>
       <c r="G60" s="3">
-        <v>2379100</v>
+        <v>2252000</v>
       </c>
       <c r="H60" s="3">
-        <v>3129200</v>
+        <v>2962100</v>
       </c>
       <c r="I60" s="3">
-        <v>2291200</v>
+        <v>2168800</v>
       </c>
       <c r="J60" s="3">
-        <v>1963900</v>
+        <v>1859000</v>
       </c>
       <c r="K60" s="3">
         <v>1638000</v>
@@ -2842,25 +2842,25 @@
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>1409100</v>
+        <v>1333800</v>
       </c>
       <c r="E61" s="3">
-        <v>1667800</v>
+        <v>1578700</v>
       </c>
       <c r="F61" s="3">
-        <v>1784900</v>
+        <v>1689600</v>
       </c>
       <c r="G61" s="3">
-        <v>2013000</v>
+        <v>1905500</v>
       </c>
       <c r="H61" s="3">
-        <v>1021400</v>
+        <v>966800</v>
       </c>
       <c r="I61" s="3">
-        <v>773300</v>
+        <v>732000</v>
       </c>
       <c r="J61" s="3">
-        <v>875900</v>
+        <v>829100</v>
       </c>
       <c r="K61" s="3">
         <v>690700</v>
@@ -2887,25 +2887,25 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>254100</v>
+        <v>240500</v>
       </c>
       <c r="E62" s="3">
-        <v>302700</v>
+        <v>286500</v>
       </c>
       <c r="F62" s="3">
-        <v>680800</v>
+        <v>644400</v>
       </c>
       <c r="G62" s="3">
-        <v>310000</v>
+        <v>293500</v>
       </c>
       <c r="H62" s="3">
-        <v>573700</v>
+        <v>543100</v>
       </c>
       <c r="I62" s="3">
-        <v>582900</v>
+        <v>551700</v>
       </c>
       <c r="J62" s="3">
-        <v>554200</v>
+        <v>524600</v>
       </c>
       <c r="K62" s="3">
         <v>1128900</v>
@@ -3067,25 +3067,25 @@
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>4291700</v>
+        <v>4062500</v>
       </c>
       <c r="E66" s="3">
-        <v>4740900</v>
+        <v>4487700</v>
       </c>
       <c r="F66" s="3">
-        <v>5124300</v>
+        <v>4850600</v>
       </c>
       <c r="G66" s="3">
-        <v>4843000</v>
+        <v>4584300</v>
       </c>
       <c r="H66" s="3">
-        <v>4860200</v>
+        <v>4600600</v>
       </c>
       <c r="I66" s="3">
-        <v>3775000</v>
+        <v>3573300</v>
       </c>
       <c r="J66" s="3">
-        <v>3539200</v>
+        <v>3350200</v>
       </c>
       <c r="K66" s="3">
         <v>3591000</v>
@@ -3311,25 +3311,25 @@
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>2562600</v>
+        <v>2425700</v>
       </c>
       <c r="E72" s="3">
-        <v>2661500</v>
+        <v>2519300</v>
       </c>
       <c r="F72" s="3">
-        <v>4984700</v>
+        <v>4718500</v>
       </c>
       <c r="G72" s="3">
-        <v>2299800</v>
+        <v>2177000</v>
       </c>
       <c r="H72" s="3">
-        <v>2512000</v>
+        <v>2377800</v>
       </c>
       <c r="I72" s="3">
-        <v>2156500</v>
+        <v>2041300</v>
       </c>
       <c r="J72" s="3">
-        <v>1837000</v>
+        <v>1738900</v>
       </c>
       <c r="K72" s="3">
         <v>1718600</v>
@@ -3491,25 +3491,25 @@
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>4170400</v>
+        <v>3947600</v>
       </c>
       <c r="E76" s="3">
-        <v>4072700</v>
+        <v>3855200</v>
       </c>
       <c r="F76" s="3">
-        <v>3644300</v>
+        <v>3449600</v>
       </c>
       <c r="G76" s="3">
-        <v>3273500</v>
+        <v>3098700</v>
       </c>
       <c r="H76" s="3">
-        <v>3354500</v>
+        <v>3175300</v>
       </c>
       <c r="I76" s="3">
-        <v>3029900</v>
+        <v>2868000</v>
       </c>
       <c r="J76" s="3">
-        <v>2859900</v>
+        <v>2707200</v>
       </c>
       <c r="K76" s="3">
         <v>2614700</v>
@@ -3631,25 +3631,25 @@
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>146600</v>
+        <v>138800</v>
       </c>
       <c r="E81" s="3">
-        <v>230500</v>
+        <v>218200</v>
       </c>
       <c r="F81" s="3">
-        <v>299500</v>
+        <v>283500</v>
       </c>
       <c r="G81" s="3">
-        <v>-78600</v>
+        <v>-74400</v>
       </c>
       <c r="H81" s="3">
-        <v>495800</v>
+        <v>469300</v>
       </c>
       <c r="I81" s="3">
-        <v>413900</v>
+        <v>391800</v>
       </c>
       <c r="J81" s="3">
-        <v>153300</v>
+        <v>145100</v>
       </c>
       <c r="K81" s="3">
         <v>213200</v>
@@ -3695,25 +3695,25 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>508800</v>
+        <v>481600</v>
       </c>
       <c r="E83" s="3">
-        <v>510300</v>
+        <v>483100</v>
       </c>
       <c r="F83" s="3">
-        <v>558900</v>
+        <v>529000</v>
       </c>
       <c r="G83" s="3">
-        <v>454600</v>
+        <v>430300</v>
       </c>
       <c r="H83" s="3">
-        <v>393700</v>
+        <v>372700</v>
       </c>
       <c r="I83" s="3">
-        <v>295500</v>
+        <v>279700</v>
       </c>
       <c r="J83" s="3">
-        <v>295500</v>
+        <v>279800</v>
       </c>
       <c r="K83" s="3">
         <v>261600</v>
@@ -3965,25 +3965,25 @@
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>603500</v>
+        <v>571300</v>
       </c>
       <c r="E89" s="3">
-        <v>311600</v>
+        <v>295000</v>
       </c>
       <c r="F89" s="3">
-        <v>904800</v>
+        <v>856500</v>
       </c>
       <c r="G89" s="3">
-        <v>431700</v>
+        <v>408600</v>
       </c>
       <c r="H89" s="3">
-        <v>509100</v>
+        <v>481900</v>
       </c>
       <c r="I89" s="3">
-        <v>624000</v>
+        <v>590600</v>
       </c>
       <c r="J89" s="3">
-        <v>642900</v>
+        <v>608600</v>
       </c>
       <c r="K89" s="3">
         <v>392600</v>
@@ -4029,25 +4029,25 @@
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-180000</v>
+        <v>-170400</v>
       </c>
       <c r="E91" s="3">
-        <v>-244600</v>
+        <v>-231500</v>
       </c>
       <c r="F91" s="3">
-        <v>-507400</v>
+        <v>-480300</v>
       </c>
       <c r="G91" s="3">
-        <v>-379900</v>
+        <v>-359600</v>
       </c>
       <c r="H91" s="3">
-        <v>-621400</v>
+        <v>-588200</v>
       </c>
       <c r="I91" s="3">
-        <v>-543200</v>
+        <v>-514200</v>
       </c>
       <c r="J91" s="3">
-        <v>-242700</v>
+        <v>-229800</v>
       </c>
       <c r="K91" s="3">
         <v>-208300</v>
@@ -4164,25 +4164,25 @@
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-239500</v>
+        <v>-226700</v>
       </c>
       <c r="E94" s="3">
-        <v>-278400</v>
+        <v>-263500</v>
       </c>
       <c r="F94" s="3">
-        <v>449800</v>
+        <v>425800</v>
       </c>
       <c r="G94" s="3">
-        <v>-472400</v>
+        <v>-447100</v>
       </c>
       <c r="H94" s="3">
-        <v>-1367000</v>
+        <v>-1294000</v>
       </c>
       <c r="I94" s="3">
-        <v>-695000</v>
+        <v>-657900</v>
       </c>
       <c r="J94" s="3">
-        <v>-7200</v>
+        <v>-6800</v>
       </c>
       <c r="K94" s="3">
         <v>-469000</v>
@@ -4228,25 +4228,25 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-282500</v>
+        <v>-267400</v>
       </c>
       <c r="E96" s="3">
-        <v>-148100</v>
+        <v>-140200</v>
       </c>
       <c r="F96" s="3">
-        <v>-107800</v>
+        <v>-102000</v>
       </c>
       <c r="G96" s="3">
-        <v>-134600</v>
+        <v>-127400</v>
       </c>
       <c r="H96" s="3">
-        <v>-148500</v>
+        <v>-140500</v>
       </c>
       <c r="I96" s="3">
-        <v>-94000</v>
+        <v>-88900</v>
       </c>
       <c r="J96" s="3">
-        <v>-60500</v>
+        <v>-57300</v>
       </c>
       <c r="K96" s="3">
         <v>-54500</v>
@@ -4408,25 +4408,25 @@
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-509800</v>
+        <v>-482600</v>
       </c>
       <c r="E100" s="3">
-        <v>-353300</v>
+        <v>-334400</v>
       </c>
       <c r="F100" s="3">
-        <v>-1284500</v>
+        <v>-1215900</v>
       </c>
       <c r="G100" s="3">
-        <v>316000</v>
+        <v>299100</v>
       </c>
       <c r="H100" s="3">
-        <v>766200</v>
+        <v>725300</v>
       </c>
       <c r="I100" s="3">
-        <v>-200300</v>
+        <v>-189600</v>
       </c>
       <c r="J100" s="3">
-        <v>-358000</v>
+        <v>-338900</v>
       </c>
       <c r="K100" s="3">
         <v>148600</v>
@@ -4453,25 +4453,25 @@
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>49100</v>
+        <v>46400</v>
       </c>
       <c r="E101" s="3">
-        <v>67600</v>
+        <v>64000</v>
       </c>
       <c r="F101" s="3">
-        <v>65700</v>
+        <v>62200</v>
       </c>
       <c r="G101" s="3">
-        <v>-13200</v>
+        <v>-12500</v>
       </c>
       <c r="H101" s="3">
-        <v>-4700</v>
+        <v>-4400</v>
       </c>
       <c r="I101" s="3">
-        <v>-32400</v>
+        <v>-30700</v>
       </c>
       <c r="J101" s="3">
-        <v>16800</v>
+        <v>15900</v>
       </c>
       <c r="K101" s="3">
         <v>-17700</v>
@@ -4498,25 +4498,25 @@
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-96700</v>
+        <v>-91600</v>
       </c>
       <c r="E102" s="3">
-        <v>-252500</v>
+        <v>-239000</v>
       </c>
       <c r="F102" s="3">
-        <v>135800</v>
+        <v>128600</v>
       </c>
       <c r="G102" s="3">
-        <v>262100</v>
+        <v>248100</v>
       </c>
       <c r="H102" s="3">
-        <v>-96400</v>
+        <v>-91200</v>
       </c>
       <c r="I102" s="3">
-        <v>-303700</v>
+        <v>-287500</v>
       </c>
       <c r="J102" s="3">
-        <v>294600</v>
+        <v>278900</v>
       </c>
       <c r="K102" s="3">
         <v>54400</v>

--- a/AAII_Financials/Yearly/SSDOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSDOY_YR_FIN.xlsx
@@ -727,25 +727,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6208000</v>
+        <v>6908600</v>
       </c>
       <c r="E8" s="3">
-        <v>6809700</v>
+        <v>7578200</v>
       </c>
       <c r="F8" s="3">
-        <v>6443600</v>
+        <v>7170800</v>
       </c>
       <c r="G8" s="3">
-        <v>5875300</v>
+        <v>6538300</v>
       </c>
       <c r="H8" s="3">
-        <v>7219300</v>
+        <v>8034000</v>
       </c>
       <c r="I8" s="3">
-        <v>6985000</v>
+        <v>7773300</v>
       </c>
       <c r="J8" s="3">
-        <v>6412300</v>
+        <v>7135900</v>
       </c>
       <c r="K8" s="3">
         <v>5646000</v>
@@ -772,25 +772,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1656700</v>
+        <v>1843700</v>
       </c>
       <c r="E9" s="3">
-        <v>2086700</v>
+        <v>2322200</v>
       </c>
       <c r="F9" s="3">
-        <v>1734100</v>
+        <v>1929800</v>
       </c>
       <c r="G9" s="3">
-        <v>1521000</v>
+        <v>1692600</v>
       </c>
       <c r="H9" s="3">
-        <v>1625900</v>
+        <v>1809400</v>
       </c>
       <c r="I9" s="3">
-        <v>1479700</v>
+        <v>1646700</v>
       </c>
       <c r="J9" s="3">
-        <v>1475900</v>
+        <v>1642400</v>
       </c>
       <c r="K9" s="3">
         <v>1378200</v>
@@ -817,25 +817,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4551300</v>
+        <v>5064900</v>
       </c>
       <c r="E10" s="3">
-        <v>4723000</v>
+        <v>5256000</v>
       </c>
       <c r="F10" s="3">
-        <v>4709400</v>
+        <v>5240900</v>
       </c>
       <c r="G10" s="3">
-        <v>4354300</v>
+        <v>4845700</v>
       </c>
       <c r="H10" s="3">
-        <v>5593400</v>
+        <v>6224600</v>
       </c>
       <c r="I10" s="3">
-        <v>5505300</v>
+        <v>6126600</v>
       </c>
       <c r="J10" s="3">
-        <v>4936400</v>
+        <v>5493500</v>
       </c>
       <c r="K10" s="3">
         <v>4267900</v>
@@ -887,19 +887,19 @@
         <v>91</v>
       </c>
       <c r="F12" s="3">
-        <v>163400</v>
+        <v>181900</v>
       </c>
       <c r="G12" s="3">
-        <v>172200</v>
+        <v>191600</v>
       </c>
       <c r="H12" s="3">
-        <v>202200</v>
+        <v>225000</v>
       </c>
       <c r="I12" s="3">
-        <v>185800</v>
+        <v>206800</v>
       </c>
       <c r="J12" s="3">
-        <v>154600</v>
+        <v>172000</v>
       </c>
       <c r="K12" s="3">
         <v>121300</v>
@@ -971,25 +971,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>32300</v>
+        <v>36000</v>
       </c>
       <c r="E14" s="3">
-        <v>-110100</v>
+        <v>-122600</v>
       </c>
       <c r="F14" s="3">
-        <v>-506800</v>
+        <v>-564000</v>
       </c>
       <c r="G14" s="3">
-        <v>118300</v>
+        <v>131700</v>
       </c>
       <c r="H14" s="3">
-        <v>23100</v>
+        <v>25700</v>
       </c>
       <c r="I14" s="3">
-        <v>58200</v>
+        <v>64800</v>
       </c>
       <c r="J14" s="3">
-        <v>503400</v>
+        <v>560200</v>
       </c>
       <c r="K14" s="3">
         <v>31800</v>
@@ -1077,25 +1077,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>6028500</v>
+        <v>6708800</v>
       </c>
       <c r="E17" s="3">
-        <v>6512600</v>
+        <v>7247600</v>
       </c>
       <c r="F17" s="3">
-        <v>5801900</v>
+        <v>6456700</v>
       </c>
       <c r="G17" s="3">
-        <v>5898100</v>
+        <v>6563700</v>
       </c>
       <c r="H17" s="3">
-        <v>6516100</v>
+        <v>7251500</v>
       </c>
       <c r="I17" s="3">
-        <v>6351900</v>
+        <v>7068700</v>
       </c>
       <c r="J17" s="3">
-        <v>6402500</v>
+        <v>7125000</v>
       </c>
       <c r="K17" s="3">
         <v>5433600</v>
@@ -1122,25 +1122,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>179500</v>
+        <v>199700</v>
       </c>
       <c r="E18" s="3">
-        <v>297100</v>
+        <v>330700</v>
       </c>
       <c r="F18" s="3">
-        <v>641600</v>
+        <v>714100</v>
       </c>
       <c r="G18" s="3">
-        <v>-22900</v>
+        <v>-25400</v>
       </c>
       <c r="H18" s="3">
-        <v>703200</v>
+        <v>782500</v>
       </c>
       <c r="I18" s="3">
-        <v>633100</v>
+        <v>704500</v>
       </c>
       <c r="J18" s="3">
-        <v>9800</v>
+        <v>10900</v>
       </c>
       <c r="K18" s="3">
         <v>212400</v>
@@ -1186,25 +1186,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>35000</v>
+        <v>39000</v>
       </c>
       <c r="E20" s="3">
-        <v>39500</v>
+        <v>43900</v>
       </c>
       <c r="F20" s="3">
-        <v>23600</v>
+        <v>26300</v>
       </c>
       <c r="G20" s="3">
-        <v>24000</v>
+        <v>26800</v>
       </c>
       <c r="H20" s="3">
-        <v>-3500</v>
+        <v>-3900</v>
       </c>
       <c r="I20" s="3">
-        <v>37300</v>
+        <v>41500</v>
       </c>
       <c r="J20" s="3">
-        <v>242500</v>
+        <v>269900</v>
       </c>
       <c r="K20" s="3">
         <v>124100</v>
@@ -1231,25 +1231,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>695400</v>
+        <v>771000</v>
       </c>
       <c r="E21" s="3">
-        <v>818900</v>
+        <v>908400</v>
       </c>
       <c r="F21" s="3">
-        <v>1193400</v>
+        <v>1324900</v>
       </c>
       <c r="G21" s="3">
-        <v>430800</v>
+        <v>476800</v>
       </c>
       <c r="H21" s="3">
-        <v>1071800</v>
+        <v>1190400</v>
       </c>
       <c r="I21" s="3">
-        <v>949700</v>
+        <v>1055200</v>
       </c>
       <c r="J21" s="3">
-        <v>531600</v>
+        <v>589900</v>
       </c>
       <c r="K21" s="3">
         <v>596900</v>
@@ -1276,25 +1276,25 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>16500</v>
+        <v>18400</v>
       </c>
       <c r="E22" s="3">
-        <v>14900</v>
+        <v>16600</v>
       </c>
       <c r="F22" s="3">
-        <v>32900</v>
+        <v>36600</v>
       </c>
       <c r="G22" s="3">
-        <v>14200</v>
+        <v>15800</v>
       </c>
       <c r="H22" s="3">
-        <v>14600</v>
+        <v>16300</v>
       </c>
       <c r="I22" s="3">
-        <v>4900</v>
+        <v>5500</v>
       </c>
       <c r="J22" s="3">
-        <v>6300</v>
+        <v>7000</v>
       </c>
       <c r="K22" s="3">
         <v>5400</v>
@@ -1321,25 +1321,25 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>198000</v>
+        <v>220400</v>
       </c>
       <c r="E23" s="3">
-        <v>321700</v>
+        <v>358000</v>
       </c>
       <c r="F23" s="3">
-        <v>632300</v>
+        <v>703700</v>
       </c>
       <c r="G23" s="3">
-        <v>-13000</v>
+        <v>-14500</v>
       </c>
       <c r="H23" s="3">
-        <v>685100</v>
+        <v>762400</v>
       </c>
       <c r="I23" s="3">
-        <v>665500</v>
+        <v>740600</v>
       </c>
       <c r="J23" s="3">
-        <v>246000</v>
+        <v>273700</v>
       </c>
       <c r="K23" s="3">
         <v>331100</v>
@@ -1366,25 +1366,25 @@
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>43800</v>
+        <v>48700</v>
       </c>
       <c r="E24" s="3">
-        <v>82000</v>
+        <v>91200</v>
       </c>
       <c r="F24" s="3">
-        <v>316800</v>
+        <v>352600</v>
       </c>
       <c r="G24" s="3">
-        <v>45200</v>
+        <v>50300</v>
       </c>
       <c r="H24" s="3">
-        <v>191900</v>
+        <v>213500</v>
       </c>
       <c r="I24" s="3">
-        <v>251400</v>
+        <v>279800</v>
       </c>
       <c r="J24" s="3">
-        <v>84200</v>
+        <v>93700</v>
       </c>
       <c r="K24" s="3">
         <v>105800</v>
@@ -1456,25 +1456,25 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>154200</v>
+        <v>171700</v>
       </c>
       <c r="E26" s="3">
-        <v>239800</v>
+        <v>266800</v>
       </c>
       <c r="F26" s="3">
-        <v>315500</v>
+        <v>351100</v>
       </c>
       <c r="G26" s="3">
-        <v>-58200</v>
+        <v>-64700</v>
       </c>
       <c r="H26" s="3">
-        <v>493200</v>
+        <v>548800</v>
       </c>
       <c r="I26" s="3">
-        <v>414100</v>
+        <v>460800</v>
       </c>
       <c r="J26" s="3">
-        <v>161800</v>
+        <v>180000</v>
       </c>
       <c r="K26" s="3">
         <v>225300</v>
@@ -1501,25 +1501,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>138800</v>
+        <v>154400</v>
       </c>
       <c r="E27" s="3">
-        <v>218200</v>
+        <v>242800</v>
       </c>
       <c r="F27" s="3">
-        <v>283500</v>
+        <v>315500</v>
       </c>
       <c r="G27" s="3">
-        <v>-74400</v>
+        <v>-82800</v>
       </c>
       <c r="H27" s="3">
-        <v>469300</v>
+        <v>522300</v>
       </c>
       <c r="I27" s="3">
-        <v>391800</v>
+        <v>436000</v>
       </c>
       <c r="J27" s="3">
-        <v>145100</v>
+        <v>161500</v>
       </c>
       <c r="K27" s="3">
         <v>213200</v>
@@ -1726,25 +1726,25 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-35000</v>
+        <v>-39000</v>
       </c>
       <c r="E32" s="3">
-        <v>-39500</v>
+        <v>-43900</v>
       </c>
       <c r="F32" s="3">
-        <v>-23600</v>
+        <v>-26300</v>
       </c>
       <c r="G32" s="3">
-        <v>-24000</v>
+        <v>-26800</v>
       </c>
       <c r="H32" s="3">
-        <v>3500</v>
+        <v>3900</v>
       </c>
       <c r="I32" s="3">
-        <v>-37300</v>
+        <v>-41500</v>
       </c>
       <c r="J32" s="3">
-        <v>-242500</v>
+        <v>-269900</v>
       </c>
       <c r="K32" s="3">
         <v>-124100</v>
@@ -1771,25 +1771,25 @@
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>138800</v>
+        <v>154400</v>
       </c>
       <c r="E33" s="3">
-        <v>218200</v>
+        <v>242800</v>
       </c>
       <c r="F33" s="3">
-        <v>283500</v>
+        <v>315500</v>
       </c>
       <c r="G33" s="3">
-        <v>-74400</v>
+        <v>-82800</v>
       </c>
       <c r="H33" s="3">
-        <v>469300</v>
+        <v>522300</v>
       </c>
       <c r="I33" s="3">
-        <v>391800</v>
+        <v>436000</v>
       </c>
       <c r="J33" s="3">
-        <v>145100</v>
+        <v>161500</v>
       </c>
       <c r="K33" s="3">
         <v>213200</v>
@@ -1861,25 +1861,25 @@
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>138800</v>
+        <v>154400</v>
       </c>
       <c r="E35" s="3">
-        <v>218200</v>
+        <v>242800</v>
       </c>
       <c r="F35" s="3">
-        <v>283500</v>
+        <v>315500</v>
       </c>
       <c r="G35" s="3">
-        <v>-74400</v>
+        <v>-82800</v>
       </c>
       <c r="H35" s="3">
-        <v>469300</v>
+        <v>522300</v>
       </c>
       <c r="I35" s="3">
-        <v>391800</v>
+        <v>436000</v>
       </c>
       <c r="J35" s="3">
-        <v>145100</v>
+        <v>161500</v>
       </c>
       <c r="K35" s="3">
         <v>213200</v>
@@ -1994,25 +1994,25 @@
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>667900</v>
+        <v>743300</v>
       </c>
       <c r="E41" s="3">
-        <v>759400</v>
+        <v>845200</v>
       </c>
       <c r="F41" s="3">
-        <v>3094700</v>
+        <v>3443900</v>
       </c>
       <c r="G41" s="3">
-        <v>829500</v>
+        <v>923100</v>
       </c>
       <c r="H41" s="3">
-        <v>704000</v>
+        <v>783400</v>
       </c>
       <c r="I41" s="3">
-        <v>803200</v>
+        <v>893800</v>
       </c>
       <c r="J41" s="3">
-        <v>1063500</v>
+        <v>1183600</v>
       </c>
       <c r="K41" s="3">
         <v>797600</v>
@@ -2039,16 +2039,16 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>140100</v>
+        <v>155900</v>
       </c>
       <c r="E42" s="3">
-        <v>118000</v>
+        <v>131300</v>
       </c>
       <c r="F42" s="3">
-        <v>104800</v>
+        <v>116600</v>
       </c>
       <c r="G42" s="3">
-        <v>134000</v>
+        <v>149100</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>91</v>
@@ -2057,7 +2057,7 @@
         <v>91</v>
       </c>
       <c r="J42" s="3">
-        <v>49600</v>
+        <v>55200</v>
       </c>
       <c r="K42" s="3">
         <v>52500</v>
@@ -2084,25 +2084,25 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>955000</v>
+        <v>1062800</v>
       </c>
       <c r="E43" s="3">
-        <v>1161600</v>
+        <v>1292700</v>
       </c>
       <c r="F43" s="3">
-        <v>2964600</v>
+        <v>3299100</v>
       </c>
       <c r="G43" s="3">
-        <v>900100</v>
+        <v>1001700</v>
       </c>
       <c r="H43" s="3">
-        <v>1085600</v>
+        <v>1208200</v>
       </c>
       <c r="I43" s="3">
-        <v>1049500</v>
+        <v>1168000</v>
       </c>
       <c r="J43" s="3">
-        <v>1022900</v>
+        <v>1138400</v>
       </c>
       <c r="K43" s="3">
         <v>895300</v>
@@ -2129,25 +2129,25 @@
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>954700</v>
+        <v>1062500</v>
       </c>
       <c r="E44" s="3">
-        <v>835400</v>
+        <v>929700</v>
       </c>
       <c r="F44" s="3">
-        <v>2628900</v>
+        <v>2925600</v>
       </c>
       <c r="G44" s="3">
-        <v>1084800</v>
+        <v>1207200</v>
       </c>
       <c r="H44" s="3">
-        <v>1155400</v>
+        <v>1285800</v>
       </c>
       <c r="I44" s="3">
-        <v>955600</v>
+        <v>1063500</v>
       </c>
       <c r="J44" s="3">
-        <v>829100</v>
+        <v>922700</v>
       </c>
       <c r="K44" s="3">
         <v>1536100</v>
@@ -2174,25 +2174,25 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>281000</v>
+        <v>312700</v>
       </c>
       <c r="E45" s="3">
-        <v>470100</v>
+        <v>523200</v>
       </c>
       <c r="F45" s="3">
-        <v>300200</v>
+        <v>334100</v>
       </c>
       <c r="G45" s="3">
-        <v>335800</v>
+        <v>373700</v>
       </c>
       <c r="H45" s="3">
-        <v>453100</v>
+        <v>504200</v>
       </c>
       <c r="I45" s="3">
-        <v>462600</v>
+        <v>514800</v>
       </c>
       <c r="J45" s="3">
-        <v>392200</v>
+        <v>436500</v>
       </c>
       <c r="K45" s="3">
         <v>354300</v>
@@ -2219,25 +2219,25 @@
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>2998700</v>
+        <v>3337100</v>
       </c>
       <c r="E46" s="3">
-        <v>3344600</v>
+        <v>3722000</v>
       </c>
       <c r="F46" s="3">
-        <v>3272400</v>
+        <v>3641700</v>
       </c>
       <c r="G46" s="3">
-        <v>3284200</v>
+        <v>3654800</v>
       </c>
       <c r="H46" s="3">
-        <v>3398100</v>
+        <v>3781600</v>
       </c>
       <c r="I46" s="3">
-        <v>3081500</v>
+        <v>3429300</v>
       </c>
       <c r="J46" s="3">
-        <v>3357400</v>
+        <v>3736300</v>
       </c>
       <c r="K46" s="3">
         <v>2867800</v>
@@ -2264,25 +2264,25 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>725900</v>
+        <v>807800</v>
       </c>
       <c r="E47" s="3">
-        <v>639500</v>
+        <v>711700</v>
       </c>
       <c r="F47" s="3">
-        <v>869400</v>
+        <v>967500</v>
       </c>
       <c r="G47" s="3">
-        <v>85400</v>
+        <v>95000</v>
       </c>
       <c r="H47" s="3">
-        <v>88600</v>
+        <v>98600</v>
       </c>
       <c r="I47" s="3">
-        <v>293400</v>
+        <v>326500</v>
       </c>
       <c r="J47" s="3">
-        <v>166700</v>
+        <v>185500</v>
       </c>
       <c r="K47" s="3">
         <v>332000</v>
@@ -2309,25 +2309,25 @@
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>2567200</v>
+        <v>2856900</v>
       </c>
       <c r="E48" s="3">
-        <v>2760100</v>
+        <v>3071600</v>
       </c>
       <c r="F48" s="3">
-        <v>7434700</v>
+        <v>8273700</v>
       </c>
       <c r="G48" s="3">
-        <v>2175900</v>
+        <v>2421400</v>
       </c>
       <c r="H48" s="3">
-        <v>2008100</v>
+        <v>2234800</v>
       </c>
       <c r="I48" s="3">
-        <v>1500500</v>
+        <v>1669800</v>
       </c>
       <c r="J48" s="3">
-        <v>1012400</v>
+        <v>1126600</v>
       </c>
       <c r="K48" s="3">
         <v>1037100</v>
@@ -2354,25 +2354,25 @@
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>1274800</v>
+        <v>1418600</v>
       </c>
       <c r="E49" s="3">
-        <v>1155400</v>
+        <v>1285800</v>
       </c>
       <c r="F49" s="3">
-        <v>2595500</v>
+        <v>2888400</v>
       </c>
       <c r="G49" s="3">
-        <v>1540100</v>
+        <v>1713900</v>
       </c>
       <c r="H49" s="3">
-        <v>1590000</v>
+        <v>1769400</v>
       </c>
       <c r="I49" s="3">
-        <v>1055300</v>
+        <v>1174400</v>
       </c>
       <c r="J49" s="3">
-        <v>1075600</v>
+        <v>1197000</v>
       </c>
       <c r="K49" s="3">
         <v>1635700</v>
@@ -2489,25 +2489,25 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>443500</v>
+        <v>493600</v>
       </c>
       <c r="E52" s="3">
-        <v>443300</v>
+        <v>493300</v>
       </c>
       <c r="F52" s="3">
-        <v>718600</v>
+        <v>799700</v>
       </c>
       <c r="G52" s="3">
-        <v>597400</v>
+        <v>664900</v>
       </c>
       <c r="H52" s="3">
-        <v>691100</v>
+        <v>769100</v>
       </c>
       <c r="I52" s="3">
-        <v>657600</v>
+        <v>731800</v>
       </c>
       <c r="J52" s="3">
-        <v>445200</v>
+        <v>495500</v>
       </c>
       <c r="K52" s="3">
         <v>498400</v>
@@ -2579,25 +2579,25 @@
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>8010100</v>
+        <v>8914000</v>
       </c>
       <c r="E54" s="3">
-        <v>8342900</v>
+        <v>9284400</v>
       </c>
       <c r="F54" s="3">
-        <v>8300200</v>
+        <v>9237000</v>
       </c>
       <c r="G54" s="3">
-        <v>7683000</v>
+        <v>8550000</v>
       </c>
       <c r="H54" s="3">
-        <v>7775900</v>
+        <v>8653400</v>
       </c>
       <c r="I54" s="3">
-        <v>6441400</v>
+        <v>7168300</v>
       </c>
       <c r="J54" s="3">
-        <v>6057300</v>
+        <v>6740900</v>
       </c>
       <c r="K54" s="3">
         <v>6205700</v>
@@ -2662,25 +2662,25 @@
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>640300</v>
+        <v>712600</v>
       </c>
       <c r="E57" s="3">
-        <v>681600</v>
+        <v>758500</v>
       </c>
       <c r="F57" s="3">
-        <v>2398200</v>
+        <v>2668900</v>
       </c>
       <c r="G57" s="3">
-        <v>490800</v>
+        <v>546200</v>
       </c>
       <c r="H57" s="3">
-        <v>618500</v>
+        <v>688300</v>
       </c>
       <c r="I57" s="3">
-        <v>652600</v>
+        <v>726300</v>
       </c>
       <c r="J57" s="3">
-        <v>555300</v>
+        <v>617900</v>
       </c>
       <c r="K57" s="3">
         <v>553700</v>
@@ -2707,25 +2707,25 @@
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>458800</v>
+        <v>510600</v>
       </c>
       <c r="E58" s="3">
-        <v>317400</v>
+        <v>353200</v>
       </c>
       <c r="F58" s="3">
-        <v>525800</v>
+        <v>585200</v>
       </c>
       <c r="G58" s="3">
-        <v>498100</v>
+        <v>554300</v>
       </c>
       <c r="H58" s="3">
-        <v>937400</v>
+        <v>1043200</v>
       </c>
       <c r="I58" s="3">
-        <v>97000</v>
+        <v>107900</v>
       </c>
       <c r="J58" s="3">
-        <v>68000</v>
+        <v>75700</v>
       </c>
       <c r="K58" s="3">
         <v>109900</v>
@@ -2752,25 +2752,25 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>1250900</v>
+        <v>1392000</v>
       </c>
       <c r="E59" s="3">
-        <v>1486400</v>
+        <v>1654200</v>
       </c>
       <c r="F59" s="3">
-        <v>2684900</v>
+        <v>2987900</v>
       </c>
       <c r="G59" s="3">
-        <v>1263100</v>
+        <v>1405600</v>
       </c>
       <c r="H59" s="3">
-        <v>1406200</v>
+        <v>1564900</v>
       </c>
       <c r="I59" s="3">
-        <v>1419200</v>
+        <v>1579400</v>
       </c>
       <c r="J59" s="3">
-        <v>1235700</v>
+        <v>1375200</v>
       </c>
       <c r="K59" s="3">
         <v>974300</v>
@@ -2797,25 +2797,25 @@
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>2350000</v>
+        <v>2615200</v>
       </c>
       <c r="E60" s="3">
-        <v>2485400</v>
+        <v>2765900</v>
       </c>
       <c r="F60" s="3">
-        <v>2638500</v>
+        <v>2936300</v>
       </c>
       <c r="G60" s="3">
-        <v>2252000</v>
+        <v>2506100</v>
       </c>
       <c r="H60" s="3">
-        <v>2962100</v>
+        <v>3296300</v>
       </c>
       <c r="I60" s="3">
-        <v>2168800</v>
+        <v>2413600</v>
       </c>
       <c r="J60" s="3">
-        <v>1859000</v>
+        <v>2068800</v>
       </c>
       <c r="K60" s="3">
         <v>1638000</v>
@@ -2842,25 +2842,25 @@
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>1333800</v>
+        <v>1484400</v>
       </c>
       <c r="E61" s="3">
-        <v>1578700</v>
+        <v>1756800</v>
       </c>
       <c r="F61" s="3">
-        <v>1689600</v>
+        <v>1880300</v>
       </c>
       <c r="G61" s="3">
-        <v>1905500</v>
+        <v>2120500</v>
       </c>
       <c r="H61" s="3">
-        <v>966800</v>
+        <v>1075900</v>
       </c>
       <c r="I61" s="3">
-        <v>732000</v>
+        <v>814600</v>
       </c>
       <c r="J61" s="3">
-        <v>829100</v>
+        <v>922700</v>
       </c>
       <c r="K61" s="3">
         <v>690700</v>
@@ -2887,25 +2887,25 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>240500</v>
+        <v>267600</v>
       </c>
       <c r="E62" s="3">
-        <v>286500</v>
+        <v>318800</v>
       </c>
       <c r="F62" s="3">
-        <v>644400</v>
+        <v>717100</v>
       </c>
       <c r="G62" s="3">
-        <v>293500</v>
+        <v>326600</v>
       </c>
       <c r="H62" s="3">
-        <v>543100</v>
+        <v>604400</v>
       </c>
       <c r="I62" s="3">
-        <v>551700</v>
+        <v>614000</v>
       </c>
       <c r="J62" s="3">
-        <v>524600</v>
+        <v>583800</v>
       </c>
       <c r="K62" s="3">
         <v>1128900</v>
@@ -3067,25 +3067,25 @@
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>4062500</v>
+        <v>4520900</v>
       </c>
       <c r="E66" s="3">
-        <v>4487700</v>
+        <v>4994100</v>
       </c>
       <c r="F66" s="3">
-        <v>4850600</v>
+        <v>5398000</v>
       </c>
       <c r="G66" s="3">
-        <v>4584300</v>
+        <v>5101600</v>
       </c>
       <c r="H66" s="3">
-        <v>4600600</v>
+        <v>5119800</v>
       </c>
       <c r="I66" s="3">
-        <v>3573300</v>
+        <v>3976600</v>
       </c>
       <c r="J66" s="3">
-        <v>3350200</v>
+        <v>3728200</v>
       </c>
       <c r="K66" s="3">
         <v>3591000</v>
@@ -3311,25 +3311,25 @@
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>2425700</v>
+        <v>2699500</v>
       </c>
       <c r="E72" s="3">
-        <v>2519300</v>
+        <v>2803600</v>
       </c>
       <c r="F72" s="3">
-        <v>4718500</v>
+        <v>5251000</v>
       </c>
       <c r="G72" s="3">
-        <v>2177000</v>
+        <v>2422600</v>
       </c>
       <c r="H72" s="3">
-        <v>2377800</v>
+        <v>2646200</v>
       </c>
       <c r="I72" s="3">
-        <v>2041300</v>
+        <v>2271700</v>
       </c>
       <c r="J72" s="3">
-        <v>1738900</v>
+        <v>1935100</v>
       </c>
       <c r="K72" s="3">
         <v>1718600</v>
@@ -3491,25 +3491,25 @@
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>3947600</v>
+        <v>4393100</v>
       </c>
       <c r="E76" s="3">
-        <v>3855200</v>
+        <v>4290200</v>
       </c>
       <c r="F76" s="3">
-        <v>3449600</v>
+        <v>3838900</v>
       </c>
       <c r="G76" s="3">
-        <v>3098700</v>
+        <v>3448400</v>
       </c>
       <c r="H76" s="3">
-        <v>3175300</v>
+        <v>3533700</v>
       </c>
       <c r="I76" s="3">
-        <v>2868000</v>
+        <v>3191700</v>
       </c>
       <c r="J76" s="3">
-        <v>2707200</v>
+        <v>3012700</v>
       </c>
       <c r="K76" s="3">
         <v>2614700</v>
@@ -3631,25 +3631,25 @@
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>138800</v>
+        <v>154400</v>
       </c>
       <c r="E81" s="3">
-        <v>218200</v>
+        <v>242800</v>
       </c>
       <c r="F81" s="3">
-        <v>283500</v>
+        <v>315500</v>
       </c>
       <c r="G81" s="3">
-        <v>-74400</v>
+        <v>-82800</v>
       </c>
       <c r="H81" s="3">
-        <v>469300</v>
+        <v>522300</v>
       </c>
       <c r="I81" s="3">
-        <v>391800</v>
+        <v>436000</v>
       </c>
       <c r="J81" s="3">
-        <v>145100</v>
+        <v>161500</v>
       </c>
       <c r="K81" s="3">
         <v>213200</v>
@@ -3695,25 +3695,25 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>481600</v>
+        <v>536000</v>
       </c>
       <c r="E83" s="3">
-        <v>483100</v>
+        <v>537600</v>
       </c>
       <c r="F83" s="3">
-        <v>529000</v>
+        <v>588700</v>
       </c>
       <c r="G83" s="3">
-        <v>430300</v>
+        <v>478900</v>
       </c>
       <c r="H83" s="3">
-        <v>372700</v>
+        <v>414700</v>
       </c>
       <c r="I83" s="3">
-        <v>279700</v>
+        <v>311300</v>
       </c>
       <c r="J83" s="3">
-        <v>279800</v>
+        <v>311300</v>
       </c>
       <c r="K83" s="3">
         <v>261600</v>
@@ -3965,25 +3965,25 @@
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>571300</v>
+        <v>635800</v>
       </c>
       <c r="E89" s="3">
-        <v>295000</v>
+        <v>328300</v>
       </c>
       <c r="F89" s="3">
-        <v>856500</v>
+        <v>953200</v>
       </c>
       <c r="G89" s="3">
-        <v>408600</v>
+        <v>454700</v>
       </c>
       <c r="H89" s="3">
-        <v>481900</v>
+        <v>536300</v>
       </c>
       <c r="I89" s="3">
-        <v>590600</v>
+        <v>657300</v>
       </c>
       <c r="J89" s="3">
-        <v>608600</v>
+        <v>677300</v>
       </c>
       <c r="K89" s="3">
         <v>392600</v>
@@ -4029,25 +4029,25 @@
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-170400</v>
+        <v>-189600</v>
       </c>
       <c r="E91" s="3">
-        <v>-231500</v>
+        <v>-257700</v>
       </c>
       <c r="F91" s="3">
-        <v>-480300</v>
+        <v>-534500</v>
       </c>
       <c r="G91" s="3">
-        <v>-359600</v>
+        <v>-400100</v>
       </c>
       <c r="H91" s="3">
-        <v>-588200</v>
+        <v>-654600</v>
       </c>
       <c r="I91" s="3">
-        <v>-514200</v>
+        <v>-572200</v>
       </c>
       <c r="J91" s="3">
-        <v>-229800</v>
+        <v>-255700</v>
       </c>
       <c r="K91" s="3">
         <v>-208300</v>
@@ -4164,25 +4164,25 @@
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-226700</v>
+        <v>-252300</v>
       </c>
       <c r="E94" s="3">
-        <v>-263500</v>
+        <v>-293300</v>
       </c>
       <c r="F94" s="3">
-        <v>425800</v>
+        <v>473800</v>
       </c>
       <c r="G94" s="3">
-        <v>-447100</v>
+        <v>-497600</v>
       </c>
       <c r="H94" s="3">
-        <v>-1294000</v>
+        <v>-1440000</v>
       </c>
       <c r="I94" s="3">
-        <v>-657900</v>
+        <v>-732100</v>
       </c>
       <c r="J94" s="3">
-        <v>-6800</v>
+        <v>-7500</v>
       </c>
       <c r="K94" s="3">
         <v>-469000</v>
@@ -4228,25 +4228,25 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-267400</v>
+        <v>-297500</v>
       </c>
       <c r="E96" s="3">
-        <v>-140200</v>
+        <v>-156000</v>
       </c>
       <c r="F96" s="3">
-        <v>-102000</v>
+        <v>-113500</v>
       </c>
       <c r="G96" s="3">
-        <v>-127400</v>
+        <v>-141800</v>
       </c>
       <c r="H96" s="3">
-        <v>-140500</v>
+        <v>-156400</v>
       </c>
       <c r="I96" s="3">
-        <v>-88900</v>
+        <v>-99000</v>
       </c>
       <c r="J96" s="3">
-        <v>-57300</v>
+        <v>-63700</v>
       </c>
       <c r="K96" s="3">
         <v>-54500</v>
@@ -4408,25 +4408,25 @@
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-482600</v>
+        <v>-537100</v>
       </c>
       <c r="E100" s="3">
-        <v>-334400</v>
+        <v>-372200</v>
       </c>
       <c r="F100" s="3">
-        <v>-1215900</v>
+        <v>-1353100</v>
       </c>
       <c r="G100" s="3">
-        <v>299100</v>
+        <v>332800</v>
       </c>
       <c r="H100" s="3">
-        <v>725300</v>
+        <v>807100</v>
       </c>
       <c r="I100" s="3">
-        <v>-189600</v>
+        <v>-211000</v>
       </c>
       <c r="J100" s="3">
-        <v>-338900</v>
+        <v>-377100</v>
       </c>
       <c r="K100" s="3">
         <v>148600</v>
@@ -4453,25 +4453,25 @@
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>46400</v>
+        <v>51700</v>
       </c>
       <c r="E101" s="3">
-        <v>64000</v>
+        <v>71200</v>
       </c>
       <c r="F101" s="3">
-        <v>62200</v>
+        <v>69200</v>
       </c>
       <c r="G101" s="3">
-        <v>-12500</v>
+        <v>-13900</v>
       </c>
       <c r="H101" s="3">
-        <v>-4400</v>
+        <v>-4900</v>
       </c>
       <c r="I101" s="3">
-        <v>-30700</v>
+        <v>-34100</v>
       </c>
       <c r="J101" s="3">
-        <v>15900</v>
+        <v>17700</v>
       </c>
       <c r="K101" s="3">
         <v>-17700</v>
@@ -4498,25 +4498,25 @@
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-91600</v>
+        <v>-101900</v>
       </c>
       <c r="E102" s="3">
-        <v>-239000</v>
+        <v>-266000</v>
       </c>
       <c r="F102" s="3">
-        <v>128600</v>
+        <v>143100</v>
       </c>
       <c r="G102" s="3">
-        <v>248100</v>
+        <v>276100</v>
       </c>
       <c r="H102" s="3">
-        <v>-91200</v>
+        <v>-101500</v>
       </c>
       <c r="I102" s="3">
-        <v>-287500</v>
+        <v>-320000</v>
       </c>
       <c r="J102" s="3">
-        <v>278900</v>
+        <v>310300</v>
       </c>
       <c r="K102" s="3">
         <v>54400</v>

--- a/AAII_Financials/Yearly/SSDOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSDOY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
   <si>
     <t>SSDOY</t>
   </si>
@@ -295,9 +295,6 @@
   </si>
   <si>
     <t xml:space="preserve">Change In Cash and Cash Equivalents </t>
-  </si>
-  <si>
-    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -727,25 +724,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6908600</v>
+        <v>6902800</v>
       </c>
       <c r="E8" s="3">
-        <v>7578200</v>
+        <v>8093800</v>
       </c>
       <c r="F8" s="3">
-        <v>7170800</v>
+        <v>8990600</v>
       </c>
       <c r="G8" s="3">
-        <v>6538300</v>
+        <v>8922700</v>
       </c>
       <c r="H8" s="3">
-        <v>8034000</v>
+        <v>10412000</v>
       </c>
       <c r="I8" s="3">
-        <v>7773300</v>
+        <v>9978800</v>
       </c>
       <c r="J8" s="3">
-        <v>7135900</v>
+        <v>8923200</v>
       </c>
       <c r="K8" s="3">
         <v>5646000</v>
@@ -772,25 +769,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1843700</v>
+        <v>1842200</v>
       </c>
       <c r="E9" s="3">
-        <v>2322200</v>
+        <v>2450800</v>
       </c>
       <c r="F9" s="3">
-        <v>1929800</v>
+        <v>2283900</v>
       </c>
       <c r="G9" s="3">
-        <v>1692600</v>
+        <v>2309900</v>
       </c>
       <c r="H9" s="3">
-        <v>1809400</v>
+        <v>2345000</v>
       </c>
       <c r="I9" s="3">
-        <v>1646700</v>
+        <v>2113900</v>
       </c>
       <c r="J9" s="3">
-        <v>1642400</v>
+        <v>2053800</v>
       </c>
       <c r="K9" s="3">
         <v>1378200</v>
@@ -817,25 +814,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>5064900</v>
+        <v>5060700</v>
       </c>
       <c r="E10" s="3">
-        <v>5256000</v>
+        <v>5643000</v>
       </c>
       <c r="F10" s="3">
-        <v>5240900</v>
+        <v>6706800</v>
       </c>
       <c r="G10" s="3">
-        <v>4845700</v>
+        <v>6612800</v>
       </c>
       <c r="H10" s="3">
-        <v>6224600</v>
+        <v>8067100</v>
       </c>
       <c r="I10" s="3">
-        <v>6126600</v>
+        <v>7864900</v>
       </c>
       <c r="J10" s="3">
-        <v>5493500</v>
+        <v>6869400</v>
       </c>
       <c r="K10" s="3">
         <v>4267900</v>
@@ -880,26 +877,26 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>91</v>
+      <c r="D12" s="3">
+        <v>195800</v>
+      </c>
+      <c r="E12" s="3">
+        <v>202500</v>
       </c>
       <c r="F12" s="3">
-        <v>181900</v>
+        <v>222300</v>
       </c>
       <c r="G12" s="3">
-        <v>191600</v>
+        <v>261600</v>
       </c>
       <c r="H12" s="3">
-        <v>225000</v>
+        <v>291700</v>
       </c>
       <c r="I12" s="3">
-        <v>206800</v>
+        <v>265200</v>
       </c>
       <c r="J12" s="3">
-        <v>172000</v>
+        <v>215100</v>
       </c>
       <c r="K12" s="3">
         <v>121300</v>
@@ -971,25 +968,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>36000</v>
+        <v>-39200</v>
       </c>
       <c r="E14" s="3">
-        <v>-122600</v>
+        <v>-132700</v>
       </c>
       <c r="F14" s="3">
-        <v>-564000</v>
+        <v>-246900</v>
       </c>
       <c r="G14" s="3">
-        <v>131700</v>
+        <v>113200</v>
       </c>
       <c r="H14" s="3">
-        <v>25700</v>
+        <v>12500</v>
       </c>
       <c r="I14" s="3">
-        <v>64800</v>
+        <v>47200</v>
       </c>
       <c r="J14" s="3">
-        <v>560200</v>
+        <v>370900</v>
       </c>
       <c r="K14" s="3">
         <v>31800</v>
@@ -1016,25 +1013,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>535500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>574200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>606600</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>653500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>537500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>399600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>389300</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1077,25 +1074,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>6708800</v>
+        <v>6775700</v>
       </c>
       <c r="E17" s="3">
-        <v>7247600</v>
+        <v>7907600</v>
       </c>
       <c r="F17" s="3">
-        <v>6456700</v>
+        <v>8629500</v>
       </c>
       <c r="G17" s="3">
-        <v>6563700</v>
+        <v>8777700</v>
       </c>
       <c r="H17" s="3">
-        <v>7251500</v>
+        <v>9364600</v>
       </c>
       <c r="I17" s="3">
-        <v>7068700</v>
+        <v>8991200</v>
       </c>
       <c r="J17" s="3">
-        <v>7125000</v>
+        <v>8209000</v>
       </c>
       <c r="K17" s="3">
         <v>5433600</v>
@@ -1122,25 +1119,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>199700</v>
+        <v>127100</v>
       </c>
       <c r="E18" s="3">
-        <v>330700</v>
+        <v>186200</v>
       </c>
       <c r="F18" s="3">
+        <v>361200</v>
+      </c>
+      <c r="G18" s="3">
+        <v>145000</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1047400</v>
+      </c>
+      <c r="I18" s="3">
+        <v>987600</v>
+      </c>
+      <c r="J18" s="3">
         <v>714100</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-25400</v>
-      </c>
-      <c r="H18" s="3">
-        <v>782500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>704500</v>
-      </c>
-      <c r="J18" s="3">
-        <v>10900</v>
       </c>
       <c r="K18" s="3">
         <v>212400</v>
@@ -1186,25 +1183,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>39000</v>
+        <v>-32200</v>
       </c>
       <c r="E20" s="3">
-        <v>43900</v>
+        <v>-45400</v>
       </c>
       <c r="F20" s="3">
-        <v>26300</v>
+        <v>-36200</v>
       </c>
       <c r="G20" s="3">
-        <v>26800</v>
+        <v>26000</v>
       </c>
       <c r="H20" s="3">
-        <v>-3900</v>
+        <v>28600</v>
       </c>
       <c r="I20" s="3">
-        <v>41500</v>
+        <v>-14400</v>
       </c>
       <c r="J20" s="3">
-        <v>269900</v>
+        <v>-7300</v>
       </c>
       <c r="K20" s="3">
         <v>124100</v>
@@ -1231,25 +1228,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>771000</v>
+        <v>694800</v>
       </c>
       <c r="E21" s="3">
-        <v>908400</v>
+        <v>805800</v>
       </c>
       <c r="F21" s="3">
-        <v>1324900</v>
+        <v>1004100</v>
       </c>
       <c r="G21" s="3">
-        <v>476800</v>
+        <v>772500</v>
       </c>
       <c r="H21" s="3">
-        <v>1190400</v>
+        <v>1556300</v>
       </c>
       <c r="I21" s="3">
-        <v>1055200</v>
+        <v>1401600</v>
       </c>
       <c r="J21" s="3">
-        <v>589900</v>
+        <v>1110700</v>
       </c>
       <c r="K21" s="3">
         <v>596900</v>
@@ -1276,25 +1273,25 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>18400</v>
+        <v>21500</v>
       </c>
       <c r="E22" s="3">
-        <v>16600</v>
+        <v>19800</v>
       </c>
       <c r="F22" s="3">
-        <v>36600</v>
+        <v>20900</v>
       </c>
       <c r="G22" s="3">
-        <v>15800</v>
+        <v>34500</v>
       </c>
       <c r="H22" s="3">
-        <v>16300</v>
+        <v>32700</v>
       </c>
       <c r="I22" s="3">
-        <v>5500</v>
+        <v>19700</v>
       </c>
       <c r="J22" s="3">
-        <v>7000</v>
+        <v>21100</v>
       </c>
       <c r="K22" s="3">
         <v>5400</v>
@@ -1321,25 +1318,25 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>220400</v>
+        <v>220200</v>
       </c>
       <c r="E23" s="3">
-        <v>358000</v>
+        <v>382400</v>
       </c>
       <c r="F23" s="3">
-        <v>703700</v>
+        <v>636200</v>
       </c>
       <c r="G23" s="3">
-        <v>-14500</v>
+        <v>-19800</v>
       </c>
       <c r="H23" s="3">
-        <v>762400</v>
+        <v>988000</v>
       </c>
       <c r="I23" s="3">
-        <v>740600</v>
+        <v>950700</v>
       </c>
       <c r="J23" s="3">
-        <v>273700</v>
+        <v>342300</v>
       </c>
       <c r="K23" s="3">
         <v>331100</v>
@@ -1369,22 +1366,22 @@
         <v>48700</v>
       </c>
       <c r="E24" s="3">
-        <v>91200</v>
+        <v>97400</v>
       </c>
       <c r="F24" s="3">
-        <v>352600</v>
+        <v>246200</v>
       </c>
       <c r="G24" s="3">
-        <v>50300</v>
+        <v>68600</v>
       </c>
       <c r="H24" s="3">
-        <v>213500</v>
+        <v>276700</v>
       </c>
       <c r="I24" s="3">
-        <v>279800</v>
+        <v>359200</v>
       </c>
       <c r="J24" s="3">
-        <v>93700</v>
+        <v>117200</v>
       </c>
       <c r="K24" s="3">
         <v>105800</v>
@@ -1456,25 +1453,25 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>171700</v>
+        <v>171500</v>
       </c>
       <c r="E26" s="3">
-        <v>266800</v>
+        <v>285000</v>
       </c>
       <c r="F26" s="3">
-        <v>351100</v>
+        <v>390100</v>
       </c>
       <c r="G26" s="3">
-        <v>-64700</v>
+        <v>-88400</v>
       </c>
       <c r="H26" s="3">
-        <v>548800</v>
+        <v>711300</v>
       </c>
       <c r="I26" s="3">
-        <v>460800</v>
+        <v>591600</v>
       </c>
       <c r="J26" s="3">
-        <v>180000</v>
+        <v>225100</v>
       </c>
       <c r="K26" s="3">
         <v>225300</v>
@@ -1501,25 +1498,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>154400</v>
+        <v>154300</v>
       </c>
       <c r="E27" s="3">
-        <v>242800</v>
+        <v>259400</v>
       </c>
       <c r="F27" s="3">
-        <v>315500</v>
+        <v>368600</v>
       </c>
       <c r="G27" s="3">
-        <v>-82800</v>
+        <v>-113000</v>
       </c>
       <c r="H27" s="3">
-        <v>522300</v>
+        <v>676900</v>
       </c>
       <c r="I27" s="3">
-        <v>436000</v>
+        <v>559700</v>
       </c>
       <c r="J27" s="3">
-        <v>161500</v>
+        <v>202000</v>
       </c>
       <c r="K27" s="3">
         <v>213200</v>
@@ -1726,25 +1723,25 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-39000</v>
+        <v>32200</v>
       </c>
       <c r="E32" s="3">
-        <v>-43900</v>
+        <v>45400</v>
       </c>
       <c r="F32" s="3">
-        <v>-26300</v>
+        <v>36200</v>
       </c>
       <c r="G32" s="3">
-        <v>-26800</v>
+        <v>-26000</v>
       </c>
       <c r="H32" s="3">
-        <v>3900</v>
+        <v>-28600</v>
       </c>
       <c r="I32" s="3">
-        <v>-41500</v>
+        <v>14400</v>
       </c>
       <c r="J32" s="3">
-        <v>-269900</v>
+        <v>7300</v>
       </c>
       <c r="K32" s="3">
         <v>-124100</v>
@@ -1771,25 +1768,25 @@
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>154400</v>
+        <v>154300</v>
       </c>
       <c r="E33" s="3">
-        <v>242800</v>
+        <v>259400</v>
       </c>
       <c r="F33" s="3">
-        <v>315500</v>
+        <v>368600</v>
       </c>
       <c r="G33" s="3">
-        <v>-82800</v>
+        <v>-113000</v>
       </c>
       <c r="H33" s="3">
-        <v>522300</v>
+        <v>676900</v>
       </c>
       <c r="I33" s="3">
-        <v>436000</v>
+        <v>559700</v>
       </c>
       <c r="J33" s="3">
-        <v>161500</v>
+        <v>202000</v>
       </c>
       <c r="K33" s="3">
         <v>213200</v>
@@ -1861,25 +1858,25 @@
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>154400</v>
+        <v>154300</v>
       </c>
       <c r="E35" s="3">
-        <v>242800</v>
+        <v>259400</v>
       </c>
       <c r="F35" s="3">
-        <v>315500</v>
+        <v>368600</v>
       </c>
       <c r="G35" s="3">
-        <v>-82800</v>
+        <v>-113000</v>
       </c>
       <c r="H35" s="3">
-        <v>522300</v>
+        <v>676900</v>
       </c>
       <c r="I35" s="3">
-        <v>436000</v>
+        <v>559700</v>
       </c>
       <c r="J35" s="3">
-        <v>161500</v>
+        <v>202000</v>
       </c>
       <c r="K35" s="3">
         <v>213200</v>
@@ -1994,25 +1991,25 @@
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>743300</v>
+        <v>742600</v>
       </c>
       <c r="E41" s="3">
-        <v>845200</v>
+        <v>902700</v>
       </c>
       <c r="F41" s="3">
-        <v>3443900</v>
+        <v>1494300</v>
       </c>
       <c r="G41" s="3">
-        <v>923100</v>
+        <v>1259700</v>
       </c>
       <c r="H41" s="3">
-        <v>783400</v>
+        <v>1015300</v>
       </c>
       <c r="I41" s="3">
-        <v>893800</v>
+        <v>1147400</v>
       </c>
       <c r="J41" s="3">
-        <v>1183600</v>
+        <v>1480000</v>
       </c>
       <c r="K41" s="3">
         <v>797600</v>
@@ -2039,25 +2036,25 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>155900</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>131300</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>116600</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>149100</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>91</v>
+        <v>203500</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>55200</v>
+        <v>69100</v>
       </c>
       <c r="K42" s="3">
         <v>52500</v>
@@ -2084,25 +2081,25 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>1062800</v>
+        <v>1061900</v>
       </c>
       <c r="E43" s="3">
-        <v>1292700</v>
+        <v>1380600</v>
       </c>
       <c r="F43" s="3">
-        <v>3299100</v>
+        <v>1277400</v>
       </c>
       <c r="G43" s="3">
-        <v>1001700</v>
+        <v>1367000</v>
       </c>
       <c r="H43" s="3">
-        <v>1208200</v>
+        <v>1565800</v>
       </c>
       <c r="I43" s="3">
-        <v>1168000</v>
+        <v>1499400</v>
       </c>
       <c r="J43" s="3">
-        <v>1138400</v>
+        <v>1423500</v>
       </c>
       <c r="K43" s="3">
         <v>895300</v>
@@ -2129,25 +2126,25 @@
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>1062500</v>
+        <v>1061600</v>
       </c>
       <c r="E44" s="3">
-        <v>929700</v>
+        <v>992900</v>
       </c>
       <c r="F44" s="3">
-        <v>2925600</v>
+        <v>1248600</v>
       </c>
       <c r="G44" s="3">
-        <v>1207200</v>
+        <v>1647500</v>
       </c>
       <c r="H44" s="3">
-        <v>1285800</v>
+        <v>1666400</v>
       </c>
       <c r="I44" s="3">
-        <v>1063500</v>
+        <v>1365200</v>
       </c>
       <c r="J44" s="3">
-        <v>922700</v>
+        <v>1153800</v>
       </c>
       <c r="K44" s="3">
         <v>1536100</v>
@@ -2174,25 +2171,25 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>312700</v>
+        <v>373600</v>
       </c>
       <c r="E45" s="3">
-        <v>523200</v>
+        <v>615000</v>
       </c>
       <c r="F45" s="3">
-        <v>334100</v>
+        <v>509300</v>
       </c>
       <c r="G45" s="3">
-        <v>373700</v>
+        <v>510000</v>
       </c>
       <c r="H45" s="3">
-        <v>504200</v>
+        <v>653400</v>
       </c>
       <c r="I45" s="3">
-        <v>514800</v>
+        <v>390200</v>
       </c>
       <c r="J45" s="3">
-        <v>436500</v>
+        <v>319700</v>
       </c>
       <c r="K45" s="3">
         <v>354300</v>
@@ -2219,25 +2216,25 @@
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>3337100</v>
+        <v>3334300</v>
       </c>
       <c r="E46" s="3">
-        <v>3722000</v>
+        <v>3975300</v>
       </c>
       <c r="F46" s="3">
-        <v>3641700</v>
+        <v>4529600</v>
       </c>
       <c r="G46" s="3">
-        <v>3654800</v>
+        <v>4987700</v>
       </c>
       <c r="H46" s="3">
-        <v>3781600</v>
+        <v>4901000</v>
       </c>
       <c r="I46" s="3">
-        <v>3429300</v>
+        <v>4672900</v>
       </c>
       <c r="J46" s="3">
-        <v>3736300</v>
+        <v>4672100</v>
       </c>
       <c r="K46" s="3">
         <v>2867800</v>
@@ -2264,25 +2261,25 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>807800</v>
+        <v>866200</v>
       </c>
       <c r="E47" s="3">
-        <v>711700</v>
+        <v>806300</v>
       </c>
       <c r="F47" s="3">
-        <v>967500</v>
+        <v>432900</v>
       </c>
       <c r="G47" s="3">
-        <v>95000</v>
+        <v>625200</v>
       </c>
       <c r="H47" s="3">
-        <v>98600</v>
+        <v>615500</v>
       </c>
       <c r="I47" s="3">
-        <v>326500</v>
+        <v>604700</v>
       </c>
       <c r="J47" s="3">
-        <v>185500</v>
+        <v>578500</v>
       </c>
       <c r="K47" s="3">
         <v>332000</v>
@@ -2309,25 +2306,25 @@
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>2856900</v>
+        <v>2854600</v>
       </c>
       <c r="E48" s="3">
-        <v>3071600</v>
+        <v>3280500</v>
       </c>
       <c r="F48" s="3">
-        <v>8273700</v>
+        <v>3104100</v>
       </c>
       <c r="G48" s="3">
-        <v>2421400</v>
+        <v>3304500</v>
       </c>
       <c r="H48" s="3">
-        <v>2234800</v>
+        <v>2896300</v>
       </c>
       <c r="I48" s="3">
-        <v>1669800</v>
+        <v>2143600</v>
       </c>
       <c r="J48" s="3">
-        <v>1126600</v>
+        <v>1408800</v>
       </c>
       <c r="K48" s="3">
         <v>1037100</v>
@@ -2354,25 +2351,25 @@
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>1418600</v>
+        <v>1417400</v>
       </c>
       <c r="E49" s="3">
-        <v>1285800</v>
+        <v>1373300</v>
       </c>
       <c r="F49" s="3">
-        <v>2888400</v>
+        <v>1272300</v>
       </c>
       <c r="G49" s="3">
-        <v>1713900</v>
+        <v>2338900</v>
       </c>
       <c r="H49" s="3">
-        <v>1769400</v>
+        <v>2293100</v>
       </c>
       <c r="I49" s="3">
-        <v>1174400</v>
+        <v>1507600</v>
       </c>
       <c r="J49" s="3">
-        <v>1197000</v>
+        <v>1496700</v>
       </c>
       <c r="K49" s="3">
         <v>1635700</v>
@@ -2489,25 +2486,25 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>493600</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
-        <v>493300</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>799700</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>664900</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>769100</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
-        <v>731800</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3">
-        <v>495500</v>
+        <v>0</v>
       </c>
       <c r="K52" s="3">
         <v>498400</v>
@@ -2579,25 +2576,25 @@
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>8914000</v>
+        <v>8906600</v>
       </c>
       <c r="E54" s="3">
-        <v>9284400</v>
+        <v>9916100</v>
       </c>
       <c r="F54" s="3">
-        <v>9237000</v>
+        <v>10243000</v>
       </c>
       <c r="G54" s="3">
-        <v>8550000</v>
+        <v>11668100</v>
       </c>
       <c r="H54" s="3">
-        <v>8653400</v>
+        <v>11214800</v>
       </c>
       <c r="I54" s="3">
-        <v>7168300</v>
+        <v>9202200</v>
       </c>
       <c r="J54" s="3">
-        <v>6740900</v>
+        <v>8429200</v>
       </c>
       <c r="K54" s="3">
         <v>6205700</v>
@@ -2662,25 +2659,25 @@
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>712600</v>
+        <v>1266500</v>
       </c>
       <c r="E57" s="3">
-        <v>758500</v>
+        <v>1545200</v>
       </c>
       <c r="F57" s="3">
-        <v>2668900</v>
+        <v>595900</v>
       </c>
       <c r="G57" s="3">
-        <v>546200</v>
+        <v>745400</v>
       </c>
       <c r="H57" s="3">
-        <v>688300</v>
+        <v>892000</v>
       </c>
       <c r="I57" s="3">
-        <v>726300</v>
+        <v>932300</v>
       </c>
       <c r="J57" s="3">
-        <v>617900</v>
+        <v>772700</v>
       </c>
       <c r="K57" s="3">
         <v>553700</v>
@@ -2707,25 +2704,25 @@
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>510600</v>
+        <v>510200</v>
       </c>
       <c r="E58" s="3">
-        <v>353200</v>
+        <v>377200</v>
       </c>
       <c r="F58" s="3">
-        <v>585200</v>
+        <v>220600</v>
       </c>
       <c r="G58" s="3">
-        <v>554300</v>
+        <v>732200</v>
       </c>
       <c r="H58" s="3">
-        <v>1043200</v>
+        <v>1333800</v>
       </c>
       <c r="I58" s="3">
-        <v>107900</v>
+        <v>138500</v>
       </c>
       <c r="J58" s="3">
-        <v>75700</v>
+        <v>94700</v>
       </c>
       <c r="K58" s="3">
         <v>109900</v>
@@ -2752,25 +2749,25 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>1392000</v>
+        <v>438600</v>
       </c>
       <c r="E59" s="3">
-        <v>1654200</v>
+        <v>530700</v>
       </c>
       <c r="F59" s="3">
-        <v>2987900</v>
+        <v>2260800</v>
       </c>
       <c r="G59" s="3">
-        <v>1405600</v>
+        <v>1795400</v>
       </c>
       <c r="H59" s="3">
-        <v>1564900</v>
+        <v>1814100</v>
       </c>
       <c r="I59" s="3">
-        <v>1579400</v>
+        <v>1745000</v>
       </c>
       <c r="J59" s="3">
-        <v>1375200</v>
+        <v>1496400</v>
       </c>
       <c r="K59" s="3">
         <v>974300</v>
@@ -2797,25 +2794,25 @@
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>2615200</v>
+        <v>2613100</v>
       </c>
       <c r="E60" s="3">
-        <v>2765900</v>
+        <v>2942400</v>
       </c>
       <c r="F60" s="3">
-        <v>2936300</v>
+        <v>3335400</v>
       </c>
       <c r="G60" s="3">
-        <v>2506100</v>
+        <v>3420100</v>
       </c>
       <c r="H60" s="3">
-        <v>3296300</v>
+        <v>4272000</v>
       </c>
       <c r="I60" s="3">
-        <v>2413600</v>
+        <v>3098400</v>
       </c>
       <c r="J60" s="3">
-        <v>2068800</v>
+        <v>2586900</v>
       </c>
       <c r="K60" s="3">
         <v>1638000</v>
@@ -2842,25 +2839,25 @@
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>1484400</v>
+        <v>1483100</v>
       </c>
       <c r="E61" s="3">
-        <v>1756800</v>
+        <v>1876400</v>
       </c>
       <c r="F61" s="3">
-        <v>1880300</v>
+        <v>1438200</v>
       </c>
       <c r="G61" s="3">
-        <v>2120500</v>
+        <v>2410000</v>
       </c>
       <c r="H61" s="3">
-        <v>1075900</v>
+        <v>949200</v>
       </c>
       <c r="I61" s="3">
-        <v>814600</v>
+        <v>552100</v>
       </c>
       <c r="J61" s="3">
-        <v>922700</v>
+        <v>628600</v>
       </c>
       <c r="K61" s="3">
         <v>690700</v>
@@ -2887,25 +2884,25 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>267600</v>
+        <v>140300</v>
       </c>
       <c r="E62" s="3">
-        <v>318800</v>
+        <v>143500</v>
       </c>
       <c r="F62" s="3">
-        <v>717100</v>
+        <v>370700</v>
       </c>
       <c r="G62" s="3">
-        <v>326600</v>
+        <v>637500</v>
       </c>
       <c r="H62" s="3">
-        <v>604400</v>
+        <v>561200</v>
       </c>
       <c r="I62" s="3">
-        <v>614000</v>
+        <v>551000</v>
       </c>
       <c r="J62" s="3">
-        <v>583800</v>
+        <v>567000</v>
       </c>
       <c r="K62" s="3">
         <v>1128900</v>
@@ -3067,25 +3064,25 @@
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>4520900</v>
+        <v>4363600</v>
       </c>
       <c r="E66" s="3">
-        <v>4994100</v>
+        <v>5170900</v>
       </c>
       <c r="F66" s="3">
-        <v>5398000</v>
+        <v>5314700</v>
       </c>
       <c r="G66" s="3">
-        <v>5101600</v>
+        <v>6759600</v>
       </c>
       <c r="H66" s="3">
-        <v>5119800</v>
+        <v>6449700</v>
       </c>
       <c r="I66" s="3">
-        <v>3976600</v>
+        <v>4932400</v>
       </c>
       <c r="J66" s="3">
-        <v>3728200</v>
+        <v>4470700</v>
       </c>
       <c r="K66" s="3">
         <v>3591000</v>
@@ -3311,25 +3308,25 @@
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>2699500</v>
+        <v>2697200</v>
       </c>
       <c r="E72" s="3">
-        <v>2803600</v>
+        <v>2994400</v>
       </c>
       <c r="F72" s="3">
-        <v>5251000</v>
+        <v>3181500</v>
       </c>
       <c r="G72" s="3">
-        <v>2422600</v>
+        <v>3292600</v>
       </c>
       <c r="H72" s="3">
-        <v>2646200</v>
+        <v>3417800</v>
       </c>
       <c r="I72" s="3">
-        <v>2271700</v>
+        <v>2907500</v>
       </c>
       <c r="J72" s="3">
-        <v>1935100</v>
+        <v>2412000</v>
       </c>
       <c r="K72" s="3">
         <v>1718600</v>
@@ -3491,25 +3488,25 @@
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>4393100</v>
+        <v>4389500</v>
       </c>
       <c r="E76" s="3">
-        <v>4290200</v>
+        <v>4582100</v>
       </c>
       <c r="F76" s="3">
-        <v>3838900</v>
+        <v>4742900</v>
       </c>
       <c r="G76" s="3">
-        <v>3448400</v>
+        <v>4706000</v>
       </c>
       <c r="H76" s="3">
-        <v>3533700</v>
+        <v>4579600</v>
       </c>
       <c r="I76" s="3">
-        <v>3191700</v>
+        <v>4097300</v>
       </c>
       <c r="J76" s="3">
-        <v>3012700</v>
+        <v>3767200</v>
       </c>
       <c r="K76" s="3">
         <v>2614700</v>
@@ -3631,25 +3628,25 @@
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>154400</v>
+        <v>154300</v>
       </c>
       <c r="E81" s="3">
-        <v>242800</v>
+        <v>259400</v>
       </c>
       <c r="F81" s="3">
-        <v>315500</v>
+        <v>368600</v>
       </c>
       <c r="G81" s="3">
-        <v>-82800</v>
+        <v>-113000</v>
       </c>
       <c r="H81" s="3">
-        <v>522300</v>
+        <v>676900</v>
       </c>
       <c r="I81" s="3">
-        <v>436000</v>
+        <v>559700</v>
       </c>
       <c r="J81" s="3">
-        <v>161500</v>
+        <v>202000</v>
       </c>
       <c r="K81" s="3">
         <v>213200</v>
@@ -3695,25 +3692,25 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>536000</v>
+        <v>535500</v>
       </c>
       <c r="E83" s="3">
-        <v>537600</v>
+        <v>574200</v>
       </c>
       <c r="F83" s="3">
-        <v>588700</v>
+        <v>547100</v>
       </c>
       <c r="G83" s="3">
-        <v>478900</v>
+        <v>585100</v>
       </c>
       <c r="H83" s="3">
-        <v>414700</v>
+        <v>512800</v>
       </c>
       <c r="I83" s="3">
-        <v>311300</v>
+        <v>382800</v>
       </c>
       <c r="J83" s="3">
-        <v>311300</v>
+        <v>351700</v>
       </c>
       <c r="K83" s="3">
         <v>261600</v>
@@ -3965,25 +3962,25 @@
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>635800</v>
+        <v>631600</v>
       </c>
       <c r="E89" s="3">
-        <v>328300</v>
+        <v>354400</v>
       </c>
       <c r="F89" s="3">
-        <v>953200</v>
+        <v>1067300</v>
       </c>
       <c r="G89" s="3">
-        <v>454700</v>
+        <v>620500</v>
       </c>
       <c r="H89" s="3">
-        <v>536300</v>
+        <v>695300</v>
       </c>
       <c r="I89" s="3">
-        <v>657300</v>
+        <v>843800</v>
       </c>
       <c r="J89" s="3">
-        <v>677300</v>
+        <v>846900</v>
       </c>
       <c r="K89" s="3">
         <v>392600</v>
@@ -4029,25 +4026,25 @@
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-189600</v>
+        <v>-189400</v>
       </c>
       <c r="E91" s="3">
-        <v>-257700</v>
+        <v>-275200</v>
       </c>
       <c r="F91" s="3">
-        <v>-534500</v>
+        <v>-629900</v>
       </c>
       <c r="G91" s="3">
-        <v>-400100</v>
+        <v>-546100</v>
       </c>
       <c r="H91" s="3">
-        <v>-654600</v>
+        <v>-848400</v>
       </c>
       <c r="I91" s="3">
-        <v>-572200</v>
+        <v>-734600</v>
       </c>
       <c r="J91" s="3">
-        <v>-255700</v>
+        <v>-319700</v>
       </c>
       <c r="K91" s="3">
         <v>-208300</v>
@@ -4164,25 +4161,25 @@
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-252300</v>
+        <v>-252100</v>
       </c>
       <c r="E94" s="3">
-        <v>-293300</v>
+        <v>-313200</v>
       </c>
       <c r="F94" s="3">
-        <v>473800</v>
+        <v>553600</v>
       </c>
       <c r="G94" s="3">
-        <v>-497600</v>
+        <v>-679100</v>
       </c>
       <c r="H94" s="3">
-        <v>-1440000</v>
+        <v>-1866300</v>
       </c>
       <c r="I94" s="3">
-        <v>-732100</v>
+        <v>-939800</v>
       </c>
       <c r="J94" s="3">
-        <v>-7500</v>
+        <v>-9400</v>
       </c>
       <c r="K94" s="3">
         <v>-469000</v>
@@ -4228,25 +4225,25 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-297500</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-156000</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-113500</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-141800</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-156400</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-99000</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>-63700</v>
+        <v>0</v>
       </c>
       <c r="K96" s="3">
         <v>-54500</v>
@@ -4408,25 +4405,25 @@
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-537100</v>
+        <v>-536600</v>
       </c>
       <c r="E100" s="3">
-        <v>-372200</v>
+        <v>-397500</v>
       </c>
       <c r="F100" s="3">
-        <v>-1353100</v>
+        <v>-1530500</v>
       </c>
       <c r="G100" s="3">
-        <v>332800</v>
+        <v>454200</v>
       </c>
       <c r="H100" s="3">
-        <v>807100</v>
+        <v>1046000</v>
       </c>
       <c r="I100" s="3">
-        <v>-211000</v>
+        <v>-270900</v>
       </c>
       <c r="J100" s="3">
-        <v>-377100</v>
+        <v>-471600</v>
       </c>
       <c r="K100" s="3">
         <v>148600</v>
@@ -4453,25 +4450,25 @@
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>51700</v>
+        <v>51600</v>
       </c>
       <c r="E101" s="3">
-        <v>71200</v>
+        <v>76000</v>
       </c>
       <c r="F101" s="3">
-        <v>69200</v>
+        <v>84700</v>
       </c>
       <c r="G101" s="3">
-        <v>-13900</v>
+        <v>-19000</v>
       </c>
       <c r="H101" s="3">
-        <v>-4900</v>
+        <v>-6400</v>
       </c>
       <c r="I101" s="3">
-        <v>-34100</v>
+        <v>-43800</v>
       </c>
       <c r="J101" s="3">
-        <v>17700</v>
+        <v>22200</v>
       </c>
       <c r="K101" s="3">
         <v>-17700</v>
@@ -4498,25 +4495,25 @@
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-101900</v>
+        <v>-105500</v>
       </c>
       <c r="E102" s="3">
-        <v>-266000</v>
+        <v>-280300</v>
       </c>
       <c r="F102" s="3">
-        <v>143100</v>
+        <v>175100</v>
       </c>
       <c r="G102" s="3">
-        <v>276100</v>
+        <v>376700</v>
       </c>
       <c r="H102" s="3">
-        <v>-101500</v>
+        <v>-131400</v>
       </c>
       <c r="I102" s="3">
-        <v>-320000</v>
+        <v>-410800</v>
       </c>
       <c r="J102" s="3">
-        <v>310300</v>
+        <v>388100</v>
       </c>
       <c r="K102" s="3">
         <v>54400</v>

--- a/AAII_Financials/Yearly/SSDOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSDOY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="92">
   <si>
     <t>SSDOY</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t xml:space="preserve">Change In Cash and Cash Equivalents </t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -653,208 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42094</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41729</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41364</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40999</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6300600</v>
+      </c>
+      <c r="E8" s="3">
         <v>6902800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8093800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8990600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8922700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10412000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9978800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8923200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5646000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5410100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6851400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7323300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6126700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6052800</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1509900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1842200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2450800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2283900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2309900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2345000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2113900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2053800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1378200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1389700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1730600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1821700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1507700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1445700</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4790700</v>
+      </c>
+      <c r="E10" s="3">
         <v>5060700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5643000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6706800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6612800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8067100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7864900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6869400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4267900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4020400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5120800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5501600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4618900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4607000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -872,53 +887,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="3">
         <v>195800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>202500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>222300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>261600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>291700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>265200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>215100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>121300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>80100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>125300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>130100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>123500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>130100</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -961,81 +980,87 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E14" s="3">
         <v>-39200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-132700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-246900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>113200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>12500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>47200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>370900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>31800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>17400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>52300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>63400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>315400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1500</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>481300</v>
+      </c>
+      <c r="E15" s="3">
         <v>535500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>574200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>606600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>653500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>537500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>399600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>389300</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1051,9 +1076,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1068,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>6255000</v>
+      </c>
+      <c r="E17" s="3">
         <v>6775700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7907600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8629500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8777700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9364600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8991200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8209000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5433600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5160500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6660400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6909600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6206600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5707100</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E18" s="3">
         <v>127100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>186200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>361200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>145000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1047400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>987600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>714100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>212400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>249600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>191000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>413600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-79900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>345600</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1177,233 +1212,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-32200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-45400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-36200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>26000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>28600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-14400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-7300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>124100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>60300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>251600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>87600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>37800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>16000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>540000</v>
+      </c>
+      <c r="E21" s="3">
         <v>694800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>805800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1004100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>772500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1556300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1401600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1110700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>596900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>562100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>778900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>867500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>297600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>682800</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>122000</v>
+      </c>
+      <c r="E22" s="3">
         <v>21500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>19800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>20900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>34500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>32700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>19700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>21100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>10600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>16600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>16100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>16200</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E23" s="3">
         <v>220200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>382400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>636200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-19800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>988000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>950700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>342300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>331100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>304100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>432000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>484600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-58200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>345500</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E24" s="3">
         <v>48700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>97400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>246200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>68600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>276700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>359200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>117200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>105800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>122600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>112900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>208400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>56700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>194100</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1446,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-59100</v>
+      </c>
+      <c r="E26" s="3">
         <v>171500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>285000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>390100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-88400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>711300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>591600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>225100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>225300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>181500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>319200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>276200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-114900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>151300</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-68800</v>
+      </c>
+      <c r="E27" s="3">
         <v>154300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>259400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>368600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-113000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>676900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>559700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>202000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>213200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>164600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>296600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>251300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-132800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>128700</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1581,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1626,9 +1689,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1671,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1716,99 +1785,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E32" s="3">
         <v>32200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>45400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>36200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-26000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-28600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>14400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>7300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-124100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-60300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-251600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-87600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-37800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-68800</v>
+      </c>
+      <c r="E33" s="3">
         <v>154300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>259400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>368600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-113000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>676900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>559700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>202000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>213200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>164600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>296600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>251300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-132800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>128700</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1851,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-68800</v>
+      </c>
+      <c r="E35" s="3">
         <v>154300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>259400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>368600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-113000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>676900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>559700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>202000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>213200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>164600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>296600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>251300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-132800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>128700</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42094</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41729</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41364</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40999</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1966,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1985,53 +2073,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>626400</v>
+      </c>
+      <c r="E41" s="3">
         <v>742600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>902700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1494300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1259700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1015300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1147400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1480000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>797600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>827900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>912700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>920400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>536300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>595400</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2045,353 +2137,377 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>203500</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>69100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>52500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>54500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>160900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>318400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>288700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>237000</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>981500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1061900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1380600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1277400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1367000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1565800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1499400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1423500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>895300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>889300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1147200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1314600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1059600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>992900</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1020900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1061600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>992900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1248600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1647500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1666400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1365200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1153800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1536100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>751000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>940000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>867200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1528700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>637800</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>410300</v>
+      </c>
+      <c r="E45" s="3">
         <v>373600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>615000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>509300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>510000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>653400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>390200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>319700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>354300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>388900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>495900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>448300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>358500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>333100</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>3039100</v>
+      </c>
+      <c r="E46" s="3">
         <v>3334300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3975300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4529600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4987700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4901000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4672900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4672100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2867800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2911700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3656800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3868900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3007400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2796000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E47" s="3">
         <v>866200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>806300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>432900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>625200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>615500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>604700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>578500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>332000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>197000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>257000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>257900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>551200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>243000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>2539700</v>
+      </c>
+      <c r="E48" s="3">
         <v>2854600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3280500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3104100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3304500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2896300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2143600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1408800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1037100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>952100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1206800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1296200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1155400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1151300</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1828000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1417400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1373300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1272300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2338900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2293100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1507600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1496700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1635700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1144300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1472300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1602300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1362300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1540200</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2434,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2479,14 +2598,17 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>697500</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -2507,26 +2629,29 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>498400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>527500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>663300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>675700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>668600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>662000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2569,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>8471200</v>
+      </c>
+      <c r="E54" s="3">
         <v>8906600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9916100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10243000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11668100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11214800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9202200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8429200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6205700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5732600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7256200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7700900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6469000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6392600</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2634,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2653,278 +2785,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>968100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1266500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1545200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>595900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>745400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>892000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>932300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>772700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>553700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>441800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>532500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>489600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>393600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>428500</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>815600</v>
+      </c>
+      <c r="E58" s="3">
         <v>510200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>377200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>220600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>732200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1333800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>138500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>94700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>109900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>134700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>666200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>615500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>356100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>86300</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>751400</v>
+      </c>
+      <c r="E59" s="3">
         <v>438600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>530700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2260800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1795400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1814100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1745000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1496400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>974300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>889600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1139400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1295300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>942800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>946200</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>2535100</v>
+      </c>
+      <c r="E60" s="3">
         <v>2613100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2942400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3335400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3420100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4272000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3098400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2586900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1638000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1466100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2338000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2400400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1692500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1461000</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1494300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1483100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1876400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1438200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2410000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>949200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>552100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>628600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>690700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>479400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>275600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>882800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1313300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1555900</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>222800</v>
+      </c>
+      <c r="E62" s="3">
         <v>140300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>143500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>370700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>637500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>561200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>551000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>567000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1128900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>856600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1036100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>970500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>722700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>681700</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2967,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3012,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3057,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>4307400</v>
+      </c>
+      <c r="E66" s="3">
         <v>4363600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5170900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5314700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6759600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6449700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4932400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4470700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3591000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2949600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3838800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4438300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3866200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3810000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3122,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3166,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3211,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3256,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3301,54 +3474,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>2269900</v>
+      </c>
+      <c r="E72" s="3">
         <v>2697200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2994400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3181500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3292600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3417800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2907500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2412000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1718600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1664700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1936400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1964200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1738600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2001100</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3391,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3436,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3481,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>4022900</v>
+      </c>
+      <c r="E76" s="3">
         <v>4389500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4582100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4742900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4706000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4579600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4097300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3767200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2614700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2783000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3417400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3262600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2602800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2582600</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3571,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42094</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41729</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41364</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40999</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-68800</v>
+      </c>
+      <c r="E81" s="3">
         <v>154300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>259400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>368600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-113000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>676900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>559700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>202000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>213200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>164600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>296600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>251300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-132800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>128700</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3686,53 +3886,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>481300</v>
+      </c>
+      <c r="E83" s="3">
         <v>535500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>574200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>547100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>585100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>512800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>382800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>351700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>261600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>261900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>335500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>367000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>339300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>321100</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3775,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3820,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3865,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3910,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3955,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>307900</v>
+      </c>
+      <c r="E89" s="3">
         <v>631600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>354400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1067300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>620500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>695300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>843800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>846900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>392600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>429200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>288100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>810300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>380100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>466500</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4020,53 +4242,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-158100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-189400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-275200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-629900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-546100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-848400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-734600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-319700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-208300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-120100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-137500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-172600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-169600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-219400</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4109,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4154,54 +4383,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-532600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-252100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-313200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>553600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-679100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1866300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-939800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-469000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-164000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>101600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-161400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-230800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-183300</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4219,13 +4454,14 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>152500</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -4246,26 +4482,29 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-54500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-54700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-70400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-134000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-179900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-176400</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4308,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4353,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4398,142 +4643,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>148600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-536600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-397500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1530500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>454200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1046000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-270900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-471600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>148600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-213800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-514700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-456100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-223700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-314700</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E101" s="3">
         <v>51600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>76000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>84700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-19000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-6400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-43800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>22200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-17700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-22100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>42400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>94700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>49900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-39500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-105500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-280300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>175100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>376700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-131400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-410800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>388100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>54400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>29200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-82400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>287400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-24600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-49800</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SSDOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSDOY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
   <si>
     <t>SSDOY</t>
   </si>
@@ -295,9 +295,6 @@
   </si>
   <si>
     <t xml:space="preserve">Change In Cash and Cash Equivalents </t>
-  </si>
-  <si>
-    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -893,8 +890,8 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>91</v>
+      <c r="D12" s="3">
+        <v>173000</v>
       </c>
       <c r="E12" s="3">
         <v>195800</v>
@@ -990,7 +987,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-2500</v>
+        <v>-8800</v>
       </c>
       <c r="E14" s="3">
         <v>-39200</v>
@@ -1103,7 +1100,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>6255000</v>
+        <v>6361600</v>
       </c>
       <c r="E17" s="3">
         <v>6775700</v>
@@ -1151,7 +1148,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>45600</v>
+        <v>-61000</v>
       </c>
       <c r="E18" s="3">
         <v>127100</v>
@@ -1219,7 +1216,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-13000</v>
+        <v>-23400</v>
       </c>
       <c r="E20" s="3">
         <v>-32200</v>
@@ -1267,7 +1264,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>540000</v>
+        <v>443700</v>
       </c>
       <c r="E21" s="3">
         <v>694800</v>
@@ -1315,7 +1312,7 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>122000</v>
+        <v>25800</v>
       </c>
       <c r="E22" s="3">
         <v>21500</v>
@@ -1795,7 +1792,7 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>13000</v>
+        <v>23400</v>
       </c>
       <c r="E32" s="3">
         <v>32200</v>
@@ -2272,7 +2269,7 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>410300</v>
+        <v>332700</v>
       </c>
       <c r="E45" s="3">
         <v>373600</v>
@@ -2368,7 +2365,7 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>18500</v>
+        <v>716000</v>
       </c>
       <c r="E47" s="3">
         <v>866200</v>
@@ -2608,7 +2605,7 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>697500</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -2888,7 +2885,7 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>751400</v>
+        <v>388100</v>
       </c>
       <c r="E59" s="3">
         <v>438600</v>
@@ -4461,7 +4458,7 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>152500</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/SSDOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSDOY_YR_FIN.xlsx
@@ -4458,25 +4458,25 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>152500</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>297300</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>166600</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>138900</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>193500</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>202700</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>127100</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/SSDOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSDOY_YR_FIN.xlsx
@@ -653,220 +653,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41729</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41364</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40999</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6186600</v>
+      </c>
+      <c r="E8" s="3">
         <v>6300600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6902800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8093800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8990600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8922700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10412000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9978800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8923200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5646000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5410100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6851400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7323300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6126700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6052800</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1447700</v>
+      </c>
+      <c r="E9" s="3">
         <v>1509900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1842200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2450800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2283900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2309900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2345000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2113900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2053800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1378200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1389700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1730600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1821700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1507700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1445700</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4738900</v>
+      </c>
+      <c r="E10" s="3">
         <v>4790700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5060700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5643000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6706800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6612800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8067100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7864900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6869400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4267900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4020400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5120800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5501600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4618900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4607000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -885,56 +897,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>173000</v>
+        <v>159700</v>
       </c>
       <c r="E12" s="3">
+        <v>161500</v>
+      </c>
+      <c r="F12" s="3">
         <v>195800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>202500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>222300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>261600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>291700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>265200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>215100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>121300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>80100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>125300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>130100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>123500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>130100</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -980,87 +996,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>310300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-8800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-39200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-132700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-246900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>113200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>12500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>47200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>370900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>31800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>17400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>52300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>63400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>315400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1500</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>481300</v>
+        <v>363100</v>
       </c>
       <c r="E15" s="3">
+        <v>385700</v>
+      </c>
+      <c r="F15" s="3">
         <v>535500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>574200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>606600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>653500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>537500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>399600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>389300</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1076,9 +1098,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1094,104 +1119,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>6361600</v>
+        <v>6064200</v>
       </c>
       <c r="E17" s="3">
+        <v>6344100</v>
+      </c>
+      <c r="F17" s="3">
         <v>6775700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7907600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8629500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8777700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9364600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8991200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8209000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5433600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5160500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6660400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6909600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6206600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5707100</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-61000</v>
+        <v>122500</v>
       </c>
       <c r="E18" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="F18" s="3">
         <v>127100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>186200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>361200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>145000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1047400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>987600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>714100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>212400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>249600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>191000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>413600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-79900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>345600</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1210,248 +1242,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-23400</v>
+        <v>6000</v>
       </c>
       <c r="E20" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="F20" s="3">
         <v>-32200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-45400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-36200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>26000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>28600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-14400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-7300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>124100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>60300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>251600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>87600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>37800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>16000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>443700</v>
+        <v>479600</v>
       </c>
       <c r="E21" s="3">
+        <v>346700</v>
+      </c>
+      <c r="F21" s="3">
         <v>694800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>805800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1004100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>772500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1556300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1401600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1110700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>596900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>562100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>778900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>867500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>297600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>682800</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>25800</v>
+        <v>28900</v>
       </c>
       <c r="E22" s="3">
+        <v>24300</v>
+      </c>
+      <c r="F22" s="3">
         <v>21500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>19800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>20900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>34500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>32700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>19700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>21100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>10600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>16600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>16100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>16200</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-176800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>220200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>382400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>636200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-19800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>988000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>950700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>342300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>331100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>304100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>432000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>484600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-58200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>345500</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>76800</v>
+      </c>
+      <c r="E24" s="3">
         <v>51100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>48700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>97400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>246200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>68600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>276700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>359200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>117200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>105800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>122600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>112900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>208400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>56700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>194100</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1497,105 +1545,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-253600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-59100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>171500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>285000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>390100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-88400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>711300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>591600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>225100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>225300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>181500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>319200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>276200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-114900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>151300</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-259500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-68800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>154300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>259400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>368600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-113000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>676900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>559700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>202000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>213200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>164600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>296600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>251300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-132800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>128700</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1641,9 +1698,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1689,9 +1749,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1737,9 +1800,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1785,105 +1851,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>23400</v>
+        <v>-6000</v>
       </c>
       <c r="E32" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F32" s="3">
         <v>32200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>45400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>36200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-26000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-28600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>14400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>7300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-124100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-60300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-251600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-87600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-37800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-16000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-259500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-68800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>154300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>259400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>368600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-113000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>676900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>559700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>202000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>213200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>164600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>296600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>251300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-132800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>128700</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1929,110 +2004,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-259500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-68800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>154300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>259400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>368600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-113000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>676900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>559700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>202000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>213200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>164600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>296600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>251300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-132800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>128700</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41729</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41364</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40999</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2051,8 +2135,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2071,64 +2156,68 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>585800</v>
+      </c>
+      <c r="E41" s="3">
         <v>626400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>742600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>902700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1494300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1259700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1015300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1147400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1480000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>797600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>827900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>912700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>920400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>536300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>595400</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>178200</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>164400</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -2137,374 +2226,398 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>203500</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>69100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>52500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>54500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>160900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>318400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>288700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>237000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>981500</v>
+        <v>1182300</v>
       </c>
       <c r="E43" s="3">
+        <v>1102700</v>
+      </c>
+      <c r="F43" s="3">
         <v>1061900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1380600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1277400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1367000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1565800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1499400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1423500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>895300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>889300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1147200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1314600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1059600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>992900</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>938400</v>
+      </c>
+      <c r="E44" s="3">
         <v>1020900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1061600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>992900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1248600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1647500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1666400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1365200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1153800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1536100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>751000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>940000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>867200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1528700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>637800</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>332700</v>
+        <v>42000</v>
       </c>
       <c r="E45" s="3">
+        <v>47100</v>
+      </c>
+      <c r="F45" s="3">
         <v>373600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>615000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>509300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>510000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>653400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>390200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>319700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>354300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>388900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>495900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>448300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>358500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>333100</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>3007300</v>
+      </c>
+      <c r="E46" s="3">
         <v>3039100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3334300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3975300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4529600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4987700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4901000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4672900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4672100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2867800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2911700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3656800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3868900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3007400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2796000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>716000</v>
+        <v>187000</v>
       </c>
       <c r="E47" s="3">
+        <v>166400</v>
+      </c>
+      <c r="F47" s="3">
         <v>866200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>806300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>432900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>625200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>615500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>604700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>578500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>332000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>197000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>257000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>257900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>551200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>243000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>2371300</v>
+      </c>
+      <c r="E48" s="3">
         <v>2539700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2854600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3280500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3104100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3304500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2896300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2143600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1408800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1037100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>952100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1206800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1296200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1155400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1151300</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1498300</v>
+      </c>
+      <c r="E49" s="3">
         <v>1828000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1417400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1373300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1272300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2338900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2293100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1507600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1496700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1635700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1144300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1472300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1602300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1362300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1540200</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2550,9 +2663,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2598,17 +2714,20 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>426400</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>275200</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
@@ -2629,26 +2748,29 @@
         <v>0</v>
       </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>498400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>527500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>663300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>675700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>668600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>662000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2694,57 +2816,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>8082600</v>
+      </c>
+      <c r="E54" s="3">
         <v>8471200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8906600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9916100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10243000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11668100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11214800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9202200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8429200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6205700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5732600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7256200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7700900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6469000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6392600</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2763,8 +2891,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2783,296 +2912,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>968100</v>
+        <v>128200</v>
       </c>
       <c r="E57" s="3">
+        <v>142100</v>
+      </c>
+      <c r="F57" s="3">
         <v>1266500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1545200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>595900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>745400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>892000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>932300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>772700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>553700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>441800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>532500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>489600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>393600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>428500</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>320200</v>
+      </c>
+      <c r="E58" s="3">
         <v>815600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>510200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>377200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>220600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>732200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1333800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>138500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>94700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>109900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>134700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>666200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>615500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>356100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>86300</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>388100</v>
+        <v>1088600</v>
       </c>
       <c r="E59" s="3">
+        <v>983200</v>
+      </c>
+      <c r="F59" s="3">
         <v>438600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>530700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2260800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1795400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1814100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1745000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1496400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>974300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>889600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1139400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1295300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>942800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>946200</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>2200400</v>
+      </c>
+      <c r="E60" s="3">
         <v>2535100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2613100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2942400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3335400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3420100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4272000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3098400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2586900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1638000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1466100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2338000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2400400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1692500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1461000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1740900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1494300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1483100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1876400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1438200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2410000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>949200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>552100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>628600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>690700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>479400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>275600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>882800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1313300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1555900</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>222800</v>
+        <v>74600</v>
       </c>
       <c r="E62" s="3">
+        <v>178400</v>
+      </c>
+      <c r="F62" s="3">
         <v>140300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>143500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>370700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>637500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>561200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>551000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>567000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1128900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>856600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1036100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>970500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>722700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>681700</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3118,9 +3266,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3166,9 +3317,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3214,57 +3368,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>4120100</v>
+      </c>
+      <c r="E66" s="3">
         <v>4307400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4363600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5170900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5314700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6759600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6449700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4932400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4470700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3591000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2949600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3838800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4438300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3866200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3810000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3283,8 +3443,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3330,9 +3491,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3378,9 +3542,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3426,9 +3593,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3474,57 +3644,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>2044900</v>
+      </c>
+      <c r="E72" s="3">
         <v>2269900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2697200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2994400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3181500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3292600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3417800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2907500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2412000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1718600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1664700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1936400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1964200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1738600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2001100</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3570,9 +3746,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3618,9 +3797,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3666,57 +3848,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>3831600</v>
+      </c>
+      <c r="E76" s="3">
         <v>4022900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4389500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4582100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4742900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4706000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4579600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4097300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3767200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2614700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2783000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3417400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3262600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2602800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2582600</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3762,110 +3950,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41729</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41364</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40999</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-259500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-68800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>154300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>259400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>368600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-113000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>676900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>559700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>202000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>213200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>164600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>296600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>251300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-132800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>128700</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3884,56 +4081,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>481300</v>
+        <v>346600</v>
       </c>
       <c r="E83" s="3">
+        <v>367200</v>
+      </c>
+      <c r="F83" s="3">
         <v>535500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>574200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>547100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>585100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>512800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>382800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>351700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>261600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>261900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>335500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>367000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>339300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>321100</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3979,9 +4180,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -4027,9 +4231,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -4075,9 +4282,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4123,9 +4333,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -4171,57 +4384,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>700900</v>
+      </c>
+      <c r="E89" s="3">
         <v>307900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>631600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>354400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1067300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>620500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>695300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>843800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>846900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>392600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>429200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>288100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>810300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>380100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>466500</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4240,56 +4459,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-161400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-158100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-189400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-275200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-629900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-546100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-848400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-734600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-319700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-208300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-120100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-137500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-172600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-169600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-219400</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4335,9 +4558,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4383,57 +4609,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-277000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-532600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-252100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-313200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>553600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-679100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1866300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-939800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-469000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-164000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>101600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-161400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-230800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-183300</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4452,56 +4684,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>76600</v>
+      </c>
+      <c r="E96" s="3">
         <v>152500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>297300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>166600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>138900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>193500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>202700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>127100</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-54500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-54700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-70400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-134000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-179900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-176400</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4547,9 +4783,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4595,9 +4834,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4643,151 +4885,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-492700</v>
+      </c>
+      <c r="E100" s="3">
         <v>148600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-536600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-397500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1530500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>454200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1046000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-270900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-471600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>148600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-213800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-514700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-456100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-223700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-314700</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E101" s="3">
         <v>36700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>51600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>76000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>84700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-19000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-6400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-43800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>22200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-17700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-22100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>42400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>94700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>49900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-18300</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-42400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-39500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-105500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-280300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>175100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>376700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-131400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-410800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>388100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>54400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>29200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-82400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>287400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-24600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-49800</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
